--- a/research/traditional_assets/database/data/spain/spain_telecom_equipment.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_telecom_equipment.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1215949159067511</v>
+        <v>0.1213246786169842</v>
       </c>
       <c r="C2">
-        <v>281.3742085266327</v>
+        <v>279.3217150051653</v>
       </c>
       <c r="D2">
-        <v>259.7742085266327</v>
+        <v>260.7037150051653</v>
       </c>
       <c r="E2">
-        <v>-120.6</v>
+        <v>-117.618</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.982</v>
       </c>
       <c r="G2">
         <v>21.6</v>
@@ -1445,28 +1445,28 @@
         <v>48.74</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1499946</v>
       </c>
       <c r="N2">
-        <v>48.74</v>
+        <v>48.5900054</v>
       </c>
       <c r="O2">
-        <v>12.185</v>
+        <v>12.14750135</v>
       </c>
       <c r="P2">
-        <v>36.555</v>
+        <v>36.44250405</v>
       </c>
       <c r="Q2">
-        <v>38.615</v>
+        <v>38.50250405000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1215949159067511</v>
+        <v>0.1221691198151356</v>
       </c>
       <c r="T2">
-        <v>1.172523243405602</v>
+        <v>1.181405995249583</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>324.9450313544622</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1213246786169842</v>
+        <v>0.1210544413272173</v>
       </c>
       <c r="C3">
-        <v>279.3217150051653</v>
+        <v>277.2758971644191</v>
       </c>
       <c r="D3">
-        <v>260.7037150051653</v>
+        <v>261.639897164419</v>
       </c>
       <c r="E3">
-        <v>-117.618</v>
+        <v>-114.636</v>
       </c>
       <c r="F3">
-        <v>2.982</v>
+        <v>5.964</v>
       </c>
       <c r="G3">
         <v>21.6</v>
@@ -1527,28 +1527,28 @@
         <v>48.74</v>
       </c>
       <c r="M3">
-        <v>0.1499946</v>
+        <v>0.2999892</v>
       </c>
       <c r="N3">
-        <v>48.5900054</v>
+        <v>48.4400108</v>
       </c>
       <c r="O3">
-        <v>12.14750135</v>
+        <v>12.1100027</v>
       </c>
       <c r="P3">
-        <v>36.44250405</v>
+        <v>36.3300081</v>
       </c>
       <c r="Q3">
-        <v>38.50250405000001</v>
+        <v>38.3900081</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1221691198151356</v>
+        <v>0.1227550421706299</v>
       </c>
       <c r="T3">
-        <v>1.181405995249583</v>
+        <v>1.190470027743443</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>324.9450313544622</v>
+        <v>162.4725156772311</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1210544413272173</v>
+        <v>0.1207842040374505</v>
       </c>
       <c r="C4">
-        <v>277.2758971644191</v>
+        <v>275.2368271803099</v>
       </c>
       <c r="D4">
-        <v>261.639897164419</v>
+        <v>262.5828271803099</v>
       </c>
       <c r="E4">
-        <v>-114.636</v>
+        <v>-111.654</v>
       </c>
       <c r="F4">
-        <v>5.964</v>
+        <v>8.946</v>
       </c>
       <c r="G4">
         <v>21.6</v>
@@ -1609,28 +1609,28 @@
         <v>48.74</v>
       </c>
       <c r="M4">
-        <v>0.2999892</v>
+        <v>0.4499838</v>
       </c>
       <c r="N4">
-        <v>48.4400108</v>
+        <v>48.2900162</v>
       </c>
       <c r="O4">
-        <v>12.1100027</v>
+        <v>12.07250405</v>
       </c>
       <c r="P4">
-        <v>36.3300081</v>
+        <v>36.21751215</v>
       </c>
       <c r="Q4">
-        <v>38.3900081</v>
+        <v>38.27751215000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1227550421706299</v>
+        <v>0.1233530453994335</v>
       </c>
       <c r="T4">
-        <v>1.190470027743443</v>
+        <v>1.199720947505216</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>162.4725156772311</v>
+        <v>108.3150104514874</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1207842040374505</v>
+        <v>0.1205139667476836</v>
       </c>
       <c r="C5">
-        <v>275.2368271803099</v>
+        <v>273.2045782729828</v>
       </c>
       <c r="D5">
-        <v>262.5828271803099</v>
+        <v>263.5325782729828</v>
       </c>
       <c r="E5">
-        <v>-111.654</v>
+        <v>-108.672</v>
       </c>
       <c r="F5">
-        <v>8.946</v>
+        <v>11.928</v>
       </c>
       <c r="G5">
         <v>21.6</v>
@@ -1691,28 +1691,28 @@
         <v>48.74</v>
       </c>
       <c r="M5">
-        <v>0.4499838</v>
+        <v>0.5999783999999999</v>
       </c>
       <c r="N5">
-        <v>48.2900162</v>
+        <v>48.1400216</v>
       </c>
       <c r="O5">
-        <v>12.07250405</v>
+        <v>12.0350054</v>
       </c>
       <c r="P5">
-        <v>36.21751215</v>
+        <v>36.1050162</v>
       </c>
       <c r="Q5">
-        <v>38.27751215000001</v>
+        <v>38.1650162</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1233530453994335</v>
+        <v>0.123963507028837</v>
       </c>
       <c r="T5">
-        <v>1.199720947505216</v>
+        <v>1.209164594762027</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>108.3150104514874</v>
+        <v>81.23625783861554</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1205139667476836</v>
+        <v>0.1202437294579167</v>
       </c>
       <c r="C6">
-        <v>273.2045782729828</v>
+        <v>271.1792247257645</v>
       </c>
       <c r="D6">
-        <v>263.5325782729828</v>
+        <v>264.4892247257645</v>
       </c>
       <c r="E6">
-        <v>-108.672</v>
+        <v>-105.69</v>
       </c>
       <c r="F6">
-        <v>11.928</v>
+        <v>14.91</v>
       </c>
       <c r="G6">
         <v>21.6</v>
@@ -1773,28 +1773,28 @@
         <v>48.74</v>
       </c>
       <c r="M6">
-        <v>0.5999783999999999</v>
+        <v>0.749973</v>
       </c>
       <c r="N6">
-        <v>48.1400216</v>
+        <v>47.990027</v>
       </c>
       <c r="O6">
-        <v>12.0350054</v>
+        <v>11.99750675</v>
       </c>
       <c r="P6">
-        <v>36.1050162</v>
+        <v>35.99252025000001</v>
       </c>
       <c r="Q6">
-        <v>38.1650162</v>
+        <v>38.05252025000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.123963507028837</v>
+        <v>0.1245868204820176</v>
       </c>
       <c r="T6">
-        <v>1.209164594762027</v>
+        <v>1.218807055645297</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>81.23625783861554</v>
+        <v>64.98900627089242</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1202437294579167</v>
+        <v>0.1199734921681498</v>
       </c>
       <c r="C7">
-        <v>271.1792247257645</v>
+        <v>269.1608419045326</v>
       </c>
       <c r="D7">
-        <v>264.4892247257645</v>
+        <v>265.4528419045325</v>
       </c>
       <c r="E7">
-        <v>-105.69</v>
+        <v>-102.708</v>
       </c>
       <c r="F7">
-        <v>14.91</v>
+        <v>17.892</v>
       </c>
       <c r="G7">
         <v>21.6</v>
@@ -1855,28 +1855,28 @@
         <v>48.74</v>
       </c>
       <c r="M7">
-        <v>0.749973</v>
+        <v>0.8999676</v>
       </c>
       <c r="N7">
-        <v>47.990027</v>
+        <v>47.84003240000001</v>
       </c>
       <c r="O7">
-        <v>11.99750675</v>
+        <v>11.9600081</v>
       </c>
       <c r="P7">
-        <v>35.99252025000001</v>
+        <v>35.8800243</v>
       </c>
       <c r="Q7">
-        <v>38.05252025000001</v>
+        <v>37.9400243</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1245868204820176</v>
+        <v>0.1252233959235636</v>
       </c>
       <c r="T7">
-        <v>1.218807055645297</v>
+        <v>1.228654675270763</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>64.98900627089242</v>
+        <v>54.15750522574369</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1199734921681498</v>
+        <v>0.119703254878383</v>
       </c>
       <c r="C8">
-        <v>269.1608419045326</v>
+        <v>267.1495062775055</v>
       </c>
       <c r="D8">
-        <v>265.4528419045325</v>
+        <v>266.4235062775055</v>
       </c>
       <c r="E8">
-        <v>-102.708</v>
+        <v>-99.726</v>
       </c>
       <c r="F8">
-        <v>17.892</v>
+        <v>20.874</v>
       </c>
       <c r="G8">
         <v>21.6</v>
@@ -1937,28 +1937,28 @@
         <v>48.74</v>
       </c>
       <c r="M8">
-        <v>0.8999676</v>
+        <v>1.0499622</v>
       </c>
       <c r="N8">
-        <v>47.84003240000001</v>
+        <v>47.6900378</v>
       </c>
       <c r="O8">
-        <v>11.9600081</v>
+        <v>11.92250945</v>
       </c>
       <c r="P8">
-        <v>35.8800243</v>
+        <v>35.76752835</v>
       </c>
       <c r="Q8">
-        <v>37.9400243</v>
+        <v>37.82752835</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1252233959235636</v>
+        <v>0.1258736611595516</v>
       </c>
       <c r="T8">
-        <v>1.228654675270763</v>
+        <v>1.238714071662369</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>54.15750522574369</v>
+        <v>46.42071876492316</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1197032548783829</v>
+        <v>0.1194330175886161</v>
       </c>
       <c r="C9">
-        <v>267.1495062775055</v>
+        <v>265.1452954354736</v>
       </c>
       <c r="D9">
-        <v>266.4235062775055</v>
+        <v>267.4012954354736</v>
       </c>
       <c r="E9">
-        <v>-99.726</v>
+        <v>-96.744</v>
       </c>
       <c r="F9">
-        <v>20.874</v>
+        <v>23.856</v>
       </c>
       <c r="G9">
         <v>21.6</v>
@@ -2019,28 +2019,28 @@
         <v>48.74</v>
       </c>
       <c r="M9">
-        <v>1.0499622</v>
+        <v>1.1999568</v>
       </c>
       <c r="N9">
-        <v>47.6900378</v>
+        <v>47.5400432</v>
       </c>
       <c r="O9">
-        <v>11.92250945</v>
+        <v>11.8850108</v>
       </c>
       <c r="P9">
-        <v>35.76752835</v>
+        <v>35.6550324</v>
       </c>
       <c r="Q9">
-        <v>37.82752835</v>
+        <v>37.7150324</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1258736611595516</v>
+        <v>0.1265380625963218</v>
       </c>
       <c r="T9">
-        <v>1.238714071662369</v>
+        <v>1.248992150584228</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>46.42071876492316</v>
+        <v>40.61812891930776</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1194330175886161</v>
+        <v>0.1191627802988492</v>
       </c>
       <c r="C10">
-        <v>265.1452954354736</v>
+        <v>263.1482881124723</v>
       </c>
       <c r="D10">
-        <v>267.4012954354736</v>
+        <v>268.3862881124723</v>
       </c>
       <c r="E10">
-        <v>-96.744</v>
+        <v>-93.762</v>
       </c>
       <c r="F10">
-        <v>23.856</v>
+        <v>26.838</v>
       </c>
       <c r="G10">
         <v>21.6</v>
@@ -2101,28 +2101,28 @@
         <v>48.74</v>
       </c>
       <c r="M10">
-        <v>1.1999568</v>
+        <v>1.3499514</v>
       </c>
       <c r="N10">
-        <v>47.5400432</v>
+        <v>47.3900486</v>
       </c>
       <c r="O10">
-        <v>11.8850108</v>
+        <v>11.84751215</v>
       </c>
       <c r="P10">
-        <v>35.6550324</v>
+        <v>35.54253645</v>
       </c>
       <c r="Q10">
-        <v>37.7150324</v>
+        <v>37.60253645</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1265380625963218</v>
+        <v>0.1272170662624716</v>
       </c>
       <c r="T10">
-        <v>1.248992150584228</v>
+        <v>1.259496121350523</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>40.61812891930776</v>
+        <v>36.10500348382912</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1191627802988492</v>
+        <v>0.1188925430090823</v>
       </c>
       <c r="C11">
-        <v>263.1482881124723</v>
+        <v>261.1585642069174</v>
       </c>
       <c r="D11">
-        <v>268.3862881124723</v>
+        <v>269.3785642069174</v>
       </c>
       <c r="E11">
-        <v>-93.762</v>
+        <v>-90.78</v>
       </c>
       <c r="F11">
-        <v>26.838</v>
+        <v>29.82</v>
       </c>
       <c r="G11">
         <v>21.6</v>
@@ -2183,28 +2183,28 @@
         <v>48.74</v>
       </c>
       <c r="M11">
-        <v>1.3499514</v>
+        <v>1.499946</v>
       </c>
       <c r="N11">
-        <v>47.3900486</v>
+        <v>47.240054</v>
       </c>
       <c r="O11">
-        <v>11.84751215</v>
+        <v>11.8100135</v>
       </c>
       <c r="P11">
-        <v>35.54253645</v>
+        <v>35.4300405</v>
       </c>
       <c r="Q11">
-        <v>37.60253645</v>
+        <v>37.49004050000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1272170662624716</v>
+        <v>0.1279111588989803</v>
       </c>
       <c r="T11">
-        <v>1.259496121350523</v>
+        <v>1.270233513689402</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>36.10500348382912</v>
+        <v>32.49450313544622</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1188925430090823</v>
+        <v>0.1186223057193154</v>
       </c>
       <c r="C12">
-        <v>261.1585642069174</v>
+        <v>259.1762048032087</v>
       </c>
       <c r="D12">
-        <v>269.3785642069174</v>
+        <v>270.3782048032087</v>
       </c>
       <c r="E12">
-        <v>-90.78</v>
+        <v>-87.798</v>
       </c>
       <c r="F12">
-        <v>29.82</v>
+        <v>32.802</v>
       </c>
       <c r="G12">
         <v>21.6</v>
@@ -2265,28 +2265,28 @@
         <v>48.74</v>
       </c>
       <c r="M12">
-        <v>1.499946</v>
+        <v>1.6499406</v>
       </c>
       <c r="N12">
-        <v>47.240054</v>
+        <v>47.0900594</v>
       </c>
       <c r="O12">
-        <v>11.8100135</v>
+        <v>11.77251485</v>
       </c>
       <c r="P12">
-        <v>35.4300405</v>
+        <v>35.31754455</v>
       </c>
       <c r="Q12">
-        <v>37.49004050000001</v>
+        <v>37.37754455</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1279111588989803</v>
+        <v>0.1286208491228263</v>
       </c>
       <c r="T12">
-        <v>1.270233513689402</v>
+        <v>1.281212195743761</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>32.49450313544621</v>
+        <v>29.54045739586019</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1186223057193154</v>
+        <v>0.1183520684295486</v>
       </c>
       <c r="C13">
-        <v>259.1762048032087</v>
+        <v>257.2012921938185</v>
       </c>
       <c r="D13">
-        <v>270.3782048032087</v>
+        <v>271.3852921938185</v>
       </c>
       <c r="E13">
-        <v>-87.798</v>
+        <v>-84.816</v>
       </c>
       <c r="F13">
-        <v>32.802</v>
+        <v>35.784</v>
       </c>
       <c r="G13">
         <v>21.6</v>
@@ -2347,28 +2347,28 @@
         <v>48.74</v>
       </c>
       <c r="M13">
-        <v>1.6499406</v>
+        <v>1.7999352</v>
       </c>
       <c r="N13">
-        <v>47.0900594</v>
+        <v>46.9400648</v>
       </c>
       <c r="O13">
-        <v>11.77251485</v>
+        <v>11.7350162</v>
       </c>
       <c r="P13">
-        <v>35.31754455</v>
+        <v>35.2050486</v>
       </c>
       <c r="Q13">
-        <v>37.37754455</v>
+        <v>37.2650486</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1286208491228263</v>
+        <v>0.1293466686699415</v>
       </c>
       <c r="T13">
-        <v>1.281212195743761</v>
+        <v>1.292440393299356</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>29.54045739586019</v>
+        <v>27.07875261287184</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1183520684295486</v>
+        <v>0.1180818311397817</v>
       </c>
       <c r="C14">
-        <v>257.2012921938185</v>
+        <v>255.2339099018734</v>
       </c>
       <c r="D14">
-        <v>271.3852921938185</v>
+        <v>272.3999099018733</v>
       </c>
       <c r="E14">
-        <v>-84.816</v>
+        <v>-81.834</v>
       </c>
       <c r="F14">
-        <v>35.784</v>
+        <v>38.766</v>
       </c>
       <c r="G14">
         <v>21.6</v>
@@ -2429,28 +2429,28 @@
         <v>48.74</v>
       </c>
       <c r="M14">
-        <v>1.7999352</v>
+        <v>1.9499298</v>
       </c>
       <c r="N14">
-        <v>46.9400648</v>
+        <v>46.7900702</v>
       </c>
       <c r="O14">
-        <v>11.7350162</v>
+        <v>11.69751755</v>
       </c>
       <c r="P14">
-        <v>35.2050486</v>
+        <v>35.09255265</v>
       </c>
       <c r="Q14">
-        <v>37.2650486</v>
+        <v>37.15255265</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1293466686699415</v>
+        <v>0.130089173723887</v>
       </c>
       <c r="T14">
-        <v>1.292440393299356</v>
+        <v>1.303926710338988</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>27.07875261287184</v>
+        <v>24.99577164265093</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1180818311397817</v>
+        <v>0.1178115938500148</v>
       </c>
       <c r="C15">
-        <v>255.2339099018734</v>
+        <v>253.274142704246</v>
       </c>
       <c r="D15">
-        <v>272.3999099018733</v>
+        <v>273.422142704246</v>
       </c>
       <c r="E15">
-        <v>-81.834</v>
+        <v>-78.85199999999999</v>
       </c>
       <c r="F15">
-        <v>38.766</v>
+        <v>41.748</v>
       </c>
       <c r="G15">
         <v>21.6</v>
@@ -2511,28 +2511,28 @@
         <v>48.74</v>
       </c>
       <c r="M15">
-        <v>1.9499298</v>
+        <v>2.0999244</v>
       </c>
       <c r="N15">
-        <v>46.7900702</v>
+        <v>46.6400756</v>
       </c>
       <c r="O15">
-        <v>11.69751755</v>
+        <v>11.6600189</v>
       </c>
       <c r="P15">
-        <v>35.09255265</v>
+        <v>34.98005670000001</v>
       </c>
       <c r="Q15">
-        <v>37.15255265</v>
+        <v>37.04005670000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.130089173723887</v>
+        <v>0.1308489463372265</v>
       </c>
       <c r="T15">
-        <v>1.303926710338988</v>
+        <v>1.315680151030704</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>24.99577164265093</v>
+        <v>23.21035938246158</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1178115938500148</v>
+        <v>0.1175413565602479</v>
       </c>
       <c r="C16">
-        <v>253.274142704246</v>
+        <v>251.3220766551687</v>
       </c>
       <c r="D16">
-        <v>273.422142704246</v>
+        <v>274.4520766551687</v>
       </c>
       <c r="E16">
-        <v>-78.85199999999999</v>
+        <v>-75.86999999999999</v>
       </c>
       <c r="F16">
-        <v>41.748</v>
+        <v>44.73</v>
       </c>
       <c r="G16">
         <v>21.6</v>
@@ -2593,28 +2593,28 @@
         <v>48.74</v>
       </c>
       <c r="M16">
-        <v>2.0999244</v>
+        <v>2.249919</v>
       </c>
       <c r="N16">
-        <v>46.6400756</v>
+        <v>46.490081</v>
       </c>
       <c r="O16">
-        <v>11.6600189</v>
+        <v>11.62252025</v>
       </c>
       <c r="P16">
-        <v>34.98005670000001</v>
+        <v>34.86756075</v>
       </c>
       <c r="Q16">
-        <v>37.04005670000001</v>
+        <v>36.92756075</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1308489463372265</v>
+        <v>0.1316265959532328</v>
       </c>
       <c r="T16">
-        <v>1.315680151030704</v>
+        <v>1.327710143268108</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>23.21035938246158</v>
+        <v>21.66300209029747</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1175413565602479</v>
+        <v>0.117271119270481</v>
       </c>
       <c r="C17">
-        <v>251.3220766551687</v>
+        <v>249.3777991103817</v>
       </c>
       <c r="D17">
-        <v>274.4520766551687</v>
+        <v>275.4897991103817</v>
       </c>
       <c r="E17">
-        <v>-75.87</v>
+        <v>-72.88800000000001</v>
       </c>
       <c r="F17">
-        <v>44.73</v>
+        <v>47.712</v>
       </c>
       <c r="G17">
         <v>21.6</v>
@@ -2675,28 +2675,28 @@
         <v>48.74</v>
       </c>
       <c r="M17">
-        <v>2.249919</v>
+        <v>2.3999136</v>
       </c>
       <c r="N17">
-        <v>46.490081</v>
+        <v>46.3400864</v>
       </c>
       <c r="O17">
-        <v>11.62252025</v>
+        <v>11.5850216</v>
       </c>
       <c r="P17">
-        <v>34.86756075</v>
+        <v>34.7550648</v>
       </c>
       <c r="Q17">
-        <v>36.92756075</v>
+        <v>36.8150648</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1316265959532328</v>
+        <v>0.1324227610362869</v>
       </c>
       <c r="T17">
-        <v>1.327710143268108</v>
+        <v>1.340026563892116</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.66300209029747</v>
+        <v>20.30906445965389</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.117271119270481</v>
+        <v>0.1170008819807142</v>
       </c>
       <c r="C18">
-        <v>249.3777991103817</v>
+        <v>247.4413987518324</v>
       </c>
       <c r="D18">
-        <v>275.4897991103817</v>
+        <v>276.5353987518324</v>
       </c>
       <c r="E18">
-        <v>-72.88800000000001</v>
+        <v>-69.90599999999999</v>
       </c>
       <c r="F18">
-        <v>47.712</v>
+        <v>50.694</v>
       </c>
       <c r="G18">
         <v>21.6</v>
@@ -2757,28 +2757,28 @@
         <v>48.74</v>
       </c>
       <c r="M18">
-        <v>2.3999136</v>
+        <v>2.5499082</v>
       </c>
       <c r="N18">
-        <v>46.3400864</v>
+        <v>46.1900918</v>
       </c>
       <c r="O18">
-        <v>11.5850216</v>
+        <v>11.54752295</v>
       </c>
       <c r="P18">
-        <v>34.7550648</v>
+        <v>34.64256885</v>
       </c>
       <c r="Q18">
-        <v>36.8150648</v>
+        <v>36.70256885000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1324227610362869</v>
+        <v>0.1332381108201376</v>
       </c>
       <c r="T18">
-        <v>1.340026563892116</v>
+        <v>1.35263976573598</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>20.30906445965389</v>
+        <v>19.11441360908601</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1170008819807142</v>
+        <v>0.1167306446909473</v>
       </c>
       <c r="C19">
-        <v>247.4413987518324</v>
+        <v>245.5129656129388</v>
       </c>
       <c r="D19">
-        <v>276.5353987518324</v>
+        <v>277.5889656129388</v>
       </c>
       <c r="E19">
-        <v>-69.90599999999999</v>
+        <v>-66.92399999999999</v>
       </c>
       <c r="F19">
-        <v>50.694</v>
+        <v>53.676</v>
       </c>
       <c r="G19">
         <v>21.6</v>
@@ -2839,28 +2839,28 @@
         <v>48.74</v>
       </c>
       <c r="M19">
-        <v>2.5499082</v>
+        <v>2.6999028</v>
       </c>
       <c r="N19">
-        <v>46.1900918</v>
+        <v>46.04009720000001</v>
       </c>
       <c r="O19">
-        <v>11.54752295</v>
+        <v>11.5100243</v>
       </c>
       <c r="P19">
-        <v>34.64256885</v>
+        <v>34.53007290000001</v>
       </c>
       <c r="Q19">
-        <v>36.70256885000001</v>
+        <v>36.59007290000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1332381108201376</v>
+        <v>0.1340733471840821</v>
       </c>
       <c r="T19">
-        <v>1.35263976573598</v>
+        <v>1.365560606649207</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>19.11441360908601</v>
+        <v>18.05250174191456</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1167306446909473</v>
+        <v>0.1164604074011804</v>
       </c>
       <c r="C20">
-        <v>245.5129656129388</v>
+        <v>243.5925911044326</v>
       </c>
       <c r="D20">
-        <v>277.5889656129388</v>
+        <v>278.6505911044326</v>
       </c>
       <c r="E20">
-        <v>-66.92400000000001</v>
+        <v>-63.94199999999999</v>
       </c>
       <c r="F20">
-        <v>53.67599999999999</v>
+        <v>56.658</v>
       </c>
       <c r="G20">
         <v>21.6</v>
@@ -2921,28 +2921,28 @@
         <v>48.74</v>
       </c>
       <c r="M20">
-        <v>2.6999028</v>
+        <v>2.8498974</v>
       </c>
       <c r="N20">
-        <v>46.04009720000001</v>
+        <v>45.8901026</v>
       </c>
       <c r="O20">
-        <v>11.5100243</v>
+        <v>11.47252565</v>
       </c>
       <c r="P20">
-        <v>34.53007290000001</v>
+        <v>34.41757695</v>
       </c>
       <c r="Q20">
-        <v>36.59007290000001</v>
+        <v>36.47757695</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1340733471840821</v>
+        <v>0.134929206668124</v>
       </c>
       <c r="T20">
-        <v>1.365560606649207</v>
+        <v>1.378800480671402</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.05250174191456</v>
+        <v>17.10237007128748</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1164604074011804</v>
+        <v>0.1161901701114136</v>
       </c>
       <c r="C21">
-        <v>243.5925911044326</v>
+        <v>241.6803680407976</v>
       </c>
       <c r="D21">
-        <v>278.6505911044326</v>
+        <v>279.7203680407976</v>
       </c>
       <c r="E21">
-        <v>-63.94199999999999</v>
+        <v>-60.95999999999999</v>
       </c>
       <c r="F21">
-        <v>56.658</v>
+        <v>59.64</v>
       </c>
       <c r="G21">
         <v>21.6</v>
@@ -3003,28 +3003,28 @@
         <v>48.74</v>
       </c>
       <c r="M21">
-        <v>2.8498974</v>
+        <v>2.999892</v>
       </c>
       <c r="N21">
-        <v>45.8901026</v>
+        <v>45.740108</v>
       </c>
       <c r="O21">
-        <v>11.47252565</v>
+        <v>11.435027</v>
       </c>
       <c r="P21">
-        <v>34.41757695</v>
+        <v>34.305081</v>
       </c>
       <c r="Q21">
-        <v>36.47757695</v>
+        <v>36.365081</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.134929206668124</v>
+        <v>0.1358064626392669</v>
       </c>
       <c r="T21">
-        <v>1.378800480671402</v>
+        <v>1.392371351544152</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.10237007128748</v>
+        <v>16.2472515677231</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1161901701114136</v>
+        <v>0.1159199328216467</v>
       </c>
       <c r="C22">
-        <v>241.6803680407976</v>
+        <v>239.7763906673196</v>
       </c>
       <c r="D22">
-        <v>279.7203680407976</v>
+        <v>280.7983906673196</v>
       </c>
       <c r="E22">
-        <v>-60.95999999999999</v>
+        <v>-57.97799999999999</v>
       </c>
       <c r="F22">
-        <v>59.64</v>
+        <v>62.62200000000001</v>
       </c>
       <c r="G22">
         <v>21.6</v>
@@ -3085,28 +3085,28 @@
         <v>48.74</v>
       </c>
       <c r="M22">
-        <v>2.999892</v>
+        <v>3.1498866</v>
       </c>
       <c r="N22">
-        <v>45.740108</v>
+        <v>45.5901134</v>
       </c>
       <c r="O22">
-        <v>11.435027</v>
+        <v>11.39752835</v>
       </c>
       <c r="P22">
-        <v>34.305081</v>
+        <v>34.19258505</v>
       </c>
       <c r="Q22">
-        <v>36.365081</v>
+        <v>36.25258505</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1358064626392669</v>
+        <v>0.1367059276223375</v>
       </c>
       <c r="T22">
-        <v>1.392371351544152</v>
+        <v>1.406285788768111</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.2472515677231</v>
+        <v>15.47357292164105</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1159199328216467</v>
+        <v>0.1156496955318798</v>
       </c>
       <c r="C23">
-        <v>239.7763906673196</v>
+        <v>237.8807546877643</v>
       </c>
       <c r="D23">
-        <v>280.7983906673196</v>
+        <v>281.8847546877643</v>
       </c>
       <c r="E23">
-        <v>-57.978</v>
+        <v>-54.996</v>
       </c>
       <c r="F23">
-        <v>62.62199999999999</v>
+        <v>65.604</v>
       </c>
       <c r="G23">
         <v>21.6</v>
@@ -3167,28 +3167,28 @@
         <v>48.74</v>
       </c>
       <c r="M23">
-        <v>3.149886599999999</v>
+        <v>3.2998812</v>
       </c>
       <c r="N23">
-        <v>45.5901134</v>
+        <v>45.4401188</v>
       </c>
       <c r="O23">
-        <v>11.39752835</v>
+        <v>11.3600297</v>
       </c>
       <c r="P23">
-        <v>34.19258505</v>
+        <v>34.0800891</v>
       </c>
       <c r="Q23">
-        <v>36.25258505</v>
+        <v>36.1400891</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1367059276223375</v>
+        <v>0.1376284558101023</v>
       </c>
       <c r="T23">
-        <v>1.406285788768111</v>
+        <v>1.42055700643371</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.47357292164105</v>
+        <v>14.7702286979301</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1156496955318798</v>
+        <v>0.1153794582421129</v>
       </c>
       <c r="C24">
-        <v>237.8807546877643</v>
+        <v>235.9935572926991</v>
       </c>
       <c r="D24">
-        <v>281.8847546877643</v>
+        <v>282.9795572926991</v>
       </c>
       <c r="E24">
-        <v>-54.996</v>
+        <v>-52.014</v>
       </c>
       <c r="F24">
-        <v>65.604</v>
+        <v>68.586</v>
       </c>
       <c r="G24">
         <v>21.6</v>
@@ -3249,28 +3249,28 @@
         <v>48.74</v>
       </c>
       <c r="M24">
-        <v>3.2998812</v>
+        <v>3.4498758</v>
       </c>
       <c r="N24">
-        <v>45.4401188</v>
+        <v>45.2901242</v>
       </c>
       <c r="O24">
-        <v>11.3600297</v>
+        <v>11.32253105</v>
       </c>
       <c r="P24">
-        <v>34.0800891</v>
+        <v>33.96759315</v>
       </c>
       <c r="Q24">
-        <v>36.1400891</v>
+        <v>36.02759315</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1376284558101023</v>
+        <v>0.1385749457689778</v>
       </c>
       <c r="T24">
-        <v>1.42055700643371</v>
+        <v>1.435198905077636</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.7702286979301</v>
+        <v>14.12804484149835</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1153794582421129</v>
+        <v>0.115109220952346</v>
       </c>
       <c r="C25">
-        <v>235.9935572926991</v>
+        <v>234.1148971884799</v>
       </c>
       <c r="D25">
-        <v>282.9795572926991</v>
+        <v>284.0828971884799</v>
       </c>
       <c r="E25">
-        <v>-52.014</v>
+        <v>-49.032</v>
       </c>
       <c r="F25">
-        <v>68.586</v>
+        <v>71.568</v>
       </c>
       <c r="G25">
         <v>21.6</v>
@@ -3331,28 +3331,28 @@
         <v>48.74</v>
       </c>
       <c r="M25">
-        <v>3.4498758</v>
+        <v>3.5998704</v>
       </c>
       <c r="N25">
-        <v>45.2901242</v>
+        <v>45.1401296</v>
       </c>
       <c r="O25">
-        <v>11.32253105</v>
+        <v>11.2850324</v>
       </c>
       <c r="P25">
-        <v>33.96759315</v>
+        <v>33.8550972</v>
       </c>
       <c r="Q25">
-        <v>36.02759315</v>
+        <v>35.91509720000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1385749457689778</v>
+        <v>0.13954634335835</v>
       </c>
       <c r="T25">
-        <v>1.435198905077636</v>
+        <v>1.45022611684377</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.12804484149835</v>
+        <v>13.53937630643592</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.115109220952346</v>
+        <v>0.1148389836625791</v>
       </c>
       <c r="C26">
-        <v>234.1148971884799</v>
+        <v>232.2448746269159</v>
       </c>
       <c r="D26">
-        <v>284.0828971884799</v>
+        <v>285.1948746269159</v>
       </c>
       <c r="E26">
-        <v>-49.032</v>
+        <v>-46.05</v>
       </c>
       <c r="F26">
-        <v>71.568</v>
+        <v>74.55</v>
       </c>
       <c r="G26">
         <v>21.6</v>
@@ -3413,28 +3413,28 @@
         <v>48.74</v>
       </c>
       <c r="M26">
-        <v>3.5998704</v>
+        <v>3.749865</v>
       </c>
       <c r="N26">
-        <v>45.1401296</v>
+        <v>44.990135</v>
       </c>
       <c r="O26">
-        <v>11.2850324</v>
+        <v>11.24753375</v>
       </c>
       <c r="P26">
-        <v>33.8550972</v>
+        <v>33.74260125</v>
       </c>
       <c r="Q26">
-        <v>35.91509720000001</v>
+        <v>35.80260125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.13954634335835</v>
+        <v>0.1405436448834388</v>
       </c>
       <c r="T26">
-        <v>1.45022611684377</v>
+        <v>1.465654054257002</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>13.53937630643592</v>
+        <v>12.99780125417849</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1148389836625791</v>
+        <v>0.1148612463728123</v>
       </c>
       <c r="C27">
-        <v>232.2448746269159</v>
+        <v>229.1709386832823</v>
       </c>
       <c r="D27">
-        <v>285.1948746269159</v>
+        <v>285.1029386832823</v>
       </c>
       <c r="E27">
-        <v>-46.05</v>
+        <v>-43.068</v>
       </c>
       <c r="F27">
-        <v>74.55</v>
+        <v>77.532</v>
       </c>
       <c r="G27">
         <v>21.6</v>
@@ -3495,45 +3495,45 @@
         <v>48.74</v>
       </c>
       <c r="M27">
-        <v>3.749865</v>
+        <v>4.0161576</v>
       </c>
       <c r="N27">
-        <v>44.990135</v>
+        <v>44.7238424</v>
       </c>
       <c r="O27">
-        <v>11.24753375</v>
+        <v>11.1809606</v>
       </c>
       <c r="P27">
-        <v>33.74260125</v>
+        <v>33.5428818</v>
       </c>
       <c r="Q27">
-        <v>35.80260125</v>
+        <v>35.60288180000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1405436448834388</v>
+        <v>0.1415679005038004</v>
       </c>
       <c r="T27">
-        <v>1.465654054257002</v>
+        <v>1.481498962951672</v>
       </c>
       <c r="U27">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y27">
-        <v>12.99780125417849</v>
+        <v>12.13597793074654</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1148612463728123</v>
+        <v>0.1146022590830454</v>
       </c>
       <c r="C28">
-        <v>229.1709386832823</v>
+        <v>227.2621307321805</v>
       </c>
       <c r="D28">
-        <v>285.1029386832823</v>
+        <v>286.1761307321805</v>
       </c>
       <c r="E28">
-        <v>-43.068</v>
+        <v>-40.086</v>
       </c>
       <c r="F28">
-        <v>77.532</v>
+        <v>80.514</v>
       </c>
       <c r="G28">
         <v>21.6</v>
@@ -3577,28 +3577,28 @@
         <v>48.74</v>
       </c>
       <c r="M28">
-        <v>4.0161576</v>
+        <v>4.1706252</v>
       </c>
       <c r="N28">
-        <v>44.7238424</v>
+        <v>44.56937480000001</v>
       </c>
       <c r="O28">
-        <v>11.1809606</v>
+        <v>11.1423437</v>
       </c>
       <c r="P28">
-        <v>33.5428818</v>
+        <v>33.42703110000001</v>
       </c>
       <c r="Q28">
-        <v>35.60288180000001</v>
+        <v>35.48703110000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1415679005038004</v>
+        <v>0.14262021792198</v>
       </c>
       <c r="T28">
-        <v>1.481498962951672</v>
+        <v>1.497777978733868</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>12.13597793074654</v>
+        <v>11.68649726664482</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1146022590830454</v>
+        <v>0.1143432717932785</v>
       </c>
       <c r="C29">
-        <v>227.2621307321805</v>
+        <v>225.36143278496</v>
       </c>
       <c r="D29">
-        <v>286.1761307321805</v>
+        <v>287.25743278496</v>
       </c>
       <c r="E29">
-        <v>-40.086</v>
+        <v>-37.10399999999998</v>
       </c>
       <c r="F29">
-        <v>80.514</v>
+        <v>83.49600000000001</v>
       </c>
       <c r="G29">
         <v>21.6</v>
@@ -3659,28 +3659,28 @@
         <v>48.74</v>
       </c>
       <c r="M29">
-        <v>4.1706252</v>
+        <v>4.3250928</v>
       </c>
       <c r="N29">
-        <v>44.56937480000001</v>
+        <v>44.4149072</v>
       </c>
       <c r="O29">
-        <v>11.1423437</v>
+        <v>11.1037268</v>
       </c>
       <c r="P29">
-        <v>33.42703110000001</v>
+        <v>33.3111804</v>
       </c>
       <c r="Q29">
-        <v>35.48703110000001</v>
+        <v>35.3711804</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.14262021792198</v>
+        <v>0.1437017663795535</v>
       </c>
       <c r="T29">
-        <v>1.497777978733868</v>
+        <v>1.514509189398902</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.68649726664482</v>
+        <v>11.26912236426465</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1143432717932785</v>
+        <v>0.1140842845035116</v>
       </c>
       <c r="C30">
-        <v>225.36143278496</v>
+        <v>223.4689371200101</v>
       </c>
       <c r="D30">
-        <v>287.25743278496</v>
+        <v>288.3469371200101</v>
       </c>
       <c r="E30">
-        <v>-37.10399999999998</v>
+        <v>-34.12199999999999</v>
       </c>
       <c r="F30">
-        <v>83.49600000000001</v>
+        <v>86.47800000000001</v>
       </c>
       <c r="G30">
         <v>21.6</v>
@@ -3741,28 +3741,28 @@
         <v>48.74</v>
       </c>
       <c r="M30">
-        <v>4.3250928</v>
+        <v>4.4795604</v>
       </c>
       <c r="N30">
-        <v>44.4149072</v>
+        <v>44.2604396</v>
       </c>
       <c r="O30">
-        <v>11.1037268</v>
+        <v>11.0651099</v>
       </c>
       <c r="P30">
-        <v>33.3111804</v>
+        <v>33.1953297</v>
       </c>
       <c r="Q30">
-        <v>35.3711804</v>
+        <v>35.2553297</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1437017663795535</v>
+        <v>0.1448137809908615</v>
       </c>
       <c r="T30">
-        <v>1.514509189398902</v>
+        <v>1.531711701772811</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.26912236426465</v>
+        <v>10.88053193791069</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1140842845035116</v>
+        <v>0.1138252972137447</v>
       </c>
       <c r="C31">
-        <v>223.4689371200101</v>
+        <v>221.5847374210165</v>
       </c>
       <c r="D31">
-        <v>288.3469371200101</v>
+        <v>289.4447374210164</v>
       </c>
       <c r="E31">
-        <v>-34.122</v>
+        <v>-31.14</v>
       </c>
       <c r="F31">
-        <v>86.47799999999999</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G31">
         <v>21.6</v>
@@ -3823,28 +3823,28 @@
         <v>48.74</v>
       </c>
       <c r="M31">
-        <v>4.4795604</v>
+        <v>4.634028</v>
       </c>
       <c r="N31">
-        <v>44.26043960000001</v>
+        <v>44.105972</v>
       </c>
       <c r="O31">
-        <v>11.0651099</v>
+        <v>11.026493</v>
       </c>
       <c r="P31">
-        <v>33.1953297</v>
+        <v>33.079479</v>
       </c>
       <c r="Q31">
-        <v>35.2553297</v>
+        <v>35.139479</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1448137809908615</v>
+        <v>0.1459575674482068</v>
       </c>
       <c r="T31">
-        <v>1.531711701772811</v>
+        <v>1.549405714500259</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.8805319379107</v>
+        <v>10.51784753998034</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1138252972137447</v>
+        <v>0.1135663099239779</v>
       </c>
       <c r="C32">
-        <v>221.5847374210165</v>
+        <v>219.7089288038149</v>
       </c>
       <c r="D32">
-        <v>289.4447374210164</v>
+        <v>290.5509288038149</v>
       </c>
       <c r="E32">
-        <v>-31.14</v>
+        <v>-28.158</v>
       </c>
       <c r="F32">
-        <v>89.45999999999999</v>
+        <v>92.44199999999999</v>
       </c>
       <c r="G32">
         <v>21.6</v>
@@ -3905,28 +3905,28 @@
         <v>48.74</v>
       </c>
       <c r="M32">
-        <v>4.634028</v>
+        <v>4.788495599999999</v>
       </c>
       <c r="N32">
-        <v>44.105972</v>
+        <v>43.9515044</v>
       </c>
       <c r="O32">
-        <v>11.026493</v>
+        <v>10.9878761</v>
       </c>
       <c r="P32">
-        <v>33.079479</v>
+        <v>32.9636283</v>
       </c>
       <c r="Q32">
-        <v>35.139479</v>
+        <v>35.02362830000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1459575674482068</v>
+        <v>0.1471345071361998</v>
       </c>
       <c r="T32">
-        <v>1.549405714500259</v>
+        <v>1.567612597161837</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.51784753998034</v>
+        <v>10.17856213546484</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1135663099239779</v>
+        <v>0.113307322634211</v>
       </c>
       <c r="C33">
-        <v>219.7089288038149</v>
+        <v>217.8416078438635</v>
       </c>
       <c r="D33">
-        <v>290.5509288038149</v>
+        <v>291.6656078438635</v>
       </c>
       <c r="E33">
-        <v>-28.158</v>
+        <v>-25.176</v>
       </c>
       <c r="F33">
-        <v>92.44199999999999</v>
+        <v>95.42399999999999</v>
       </c>
       <c r="G33">
         <v>21.6</v>
@@ -3987,28 +3987,28 @@
         <v>48.74</v>
       </c>
       <c r="M33">
-        <v>4.788495599999999</v>
+        <v>4.942963199999999</v>
       </c>
       <c r="N33">
-        <v>43.9515044</v>
+        <v>43.7970368</v>
       </c>
       <c r="O33">
-        <v>10.9878761</v>
+        <v>10.9492592</v>
       </c>
       <c r="P33">
-        <v>32.9636283</v>
+        <v>32.8477776</v>
       </c>
       <c r="Q33">
-        <v>35.02362830000001</v>
+        <v>34.9077776</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1471345071361998</v>
+        <v>0.1483460626973691</v>
       </c>
       <c r="T33">
-        <v>1.567612597161837</v>
+        <v>1.586354976372285</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.17856213546484</v>
+        <v>9.860482068731567</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.113307322634211</v>
+        <v>0.1134690853444441</v>
       </c>
       <c r="C34">
-        <v>217.8416078438635</v>
+        <v>214.1623822353532</v>
       </c>
       <c r="D34">
-        <v>291.6656078438635</v>
+        <v>290.9683822353531</v>
       </c>
       <c r="E34">
-        <v>-25.176</v>
+        <v>-22.19399999999999</v>
       </c>
       <c r="F34">
-        <v>95.42399999999999</v>
+        <v>98.40600000000001</v>
       </c>
       <c r="G34">
         <v>21.6</v>
@@ -4069,45 +4069,45 @@
         <v>48.74</v>
       </c>
       <c r="M34">
-        <v>4.942963199999999</v>
+        <v>5.264721000000001</v>
       </c>
       <c r="N34">
-        <v>43.7970368</v>
+        <v>43.475279</v>
       </c>
       <c r="O34">
-        <v>10.9492592</v>
+        <v>10.86881975</v>
       </c>
       <c r="P34">
-        <v>32.8477776</v>
+        <v>32.60645925</v>
       </c>
       <c r="Q34">
-        <v>34.9077776</v>
+        <v>34.66645925</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1483460626973691</v>
+        <v>0.1495937840961853</v>
       </c>
       <c r="T34">
-        <v>1.586354976372285</v>
+        <v>1.605656829589014</v>
       </c>
       <c r="U34">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>9.860482068731567</v>
+        <v>9.257850510976745</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1134690853444441</v>
+        <v>0.1132228480546772</v>
       </c>
       <c r="C35">
-        <v>214.1623822353532</v>
+        <v>212.2430378174992</v>
       </c>
       <c r="D35">
-        <v>290.9683822353531</v>
+        <v>292.0310378174992</v>
       </c>
       <c r="E35">
-        <v>-22.19399999999999</v>
+        <v>-19.21199999999999</v>
       </c>
       <c r="F35">
-        <v>98.40600000000001</v>
+        <v>101.388</v>
       </c>
       <c r="G35">
         <v>21.6</v>
@@ -4151,28 +4151,28 @@
         <v>48.74</v>
       </c>
       <c r="M35">
-        <v>5.264721000000001</v>
+        <v>5.424258</v>
       </c>
       <c r="N35">
-        <v>43.475279</v>
+        <v>43.315742</v>
       </c>
       <c r="O35">
-        <v>10.86881975</v>
+        <v>10.8289355</v>
       </c>
       <c r="P35">
-        <v>32.60645925</v>
+        <v>32.4868065</v>
       </c>
       <c r="Q35">
-        <v>34.66645925</v>
+        <v>34.5468065</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1495937840961853</v>
+        <v>0.1508793152343595</v>
       </c>
       <c r="T35">
-        <v>1.605656829589014</v>
+        <v>1.625543587448675</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.257850510976745</v>
+        <v>8.985560790065664</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1132228480546772</v>
+        <v>0.1129766107649104</v>
       </c>
       <c r="C36">
-        <v>212.2430378174992</v>
+        <v>210.3314837727386</v>
       </c>
       <c r="D36">
-        <v>292.0310378174992</v>
+        <v>293.1014837727386</v>
       </c>
       <c r="E36">
-        <v>-19.21199999999999</v>
+        <v>-16.22999999999999</v>
       </c>
       <c r="F36">
-        <v>101.388</v>
+        <v>104.37</v>
       </c>
       <c r="G36">
         <v>21.6</v>
@@ -4233,28 +4233,28 @@
         <v>48.74</v>
       </c>
       <c r="M36">
-        <v>5.424258</v>
+        <v>5.583795</v>
       </c>
       <c r="N36">
-        <v>43.315742</v>
+        <v>43.156205</v>
       </c>
       <c r="O36">
-        <v>10.8289355</v>
+        <v>10.78905125</v>
       </c>
       <c r="P36">
-        <v>32.4868065</v>
+        <v>32.36715375</v>
       </c>
       <c r="Q36">
-        <v>34.5468065</v>
+        <v>34.42715375</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1508793152343595</v>
+        <v>0.1522044011767852</v>
       </c>
       <c r="T36">
-        <v>1.625543587448675</v>
+        <v>1.646042245550172</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.985560790065664</v>
+        <v>8.728830481778074</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1129766107649104</v>
+        <v>0.1127303734751435</v>
       </c>
       <c r="C37">
-        <v>210.3314837727386</v>
+        <v>208.4278060835749</v>
       </c>
       <c r="D37">
-        <v>293.1014837727386</v>
+        <v>294.1798060835749</v>
       </c>
       <c r="E37">
-        <v>-16.22999999999999</v>
+        <v>-13.24799999999999</v>
       </c>
       <c r="F37">
-        <v>104.37</v>
+        <v>107.352</v>
       </c>
       <c r="G37">
         <v>21.6</v>
@@ -4315,28 +4315,28 @@
         <v>48.74</v>
       </c>
       <c r="M37">
-        <v>5.583795</v>
+        <v>5.743332</v>
       </c>
       <c r="N37">
-        <v>43.156205</v>
+        <v>42.996668</v>
       </c>
       <c r="O37">
-        <v>10.78905125</v>
+        <v>10.749167</v>
       </c>
       <c r="P37">
-        <v>32.36715375</v>
+        <v>32.247501</v>
       </c>
       <c r="Q37">
-        <v>34.42715375</v>
+        <v>34.307501</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1522044011767852</v>
+        <v>0.1535708960549117</v>
       </c>
       <c r="T37">
-        <v>1.646042245550172</v>
+        <v>1.66718148671734</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.728830481778074</v>
+        <v>8.486362968395351</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1127303734751435</v>
+        <v>0.1124841361853766</v>
       </c>
       <c r="C38">
-        <v>208.4278060835749</v>
+        <v>206.5320920025045</v>
       </c>
       <c r="D38">
-        <v>294.1798060835748</v>
+        <v>295.2660920025045</v>
       </c>
       <c r="E38">
-        <v>-13.248</v>
+        <v>-10.26600000000001</v>
       </c>
       <c r="F38">
-        <v>107.352</v>
+        <v>110.334</v>
       </c>
       <c r="G38">
         <v>21.6</v>
@@ -4397,28 +4397,28 @@
         <v>48.74</v>
       </c>
       <c r="M38">
-        <v>5.743332</v>
+        <v>5.902868999999999</v>
       </c>
       <c r="N38">
-        <v>42.996668</v>
+        <v>42.837131</v>
       </c>
       <c r="O38">
-        <v>10.749167</v>
+        <v>10.70928275</v>
       </c>
       <c r="P38">
-        <v>32.247501</v>
+        <v>32.12784825</v>
       </c>
       <c r="Q38">
-        <v>34.307501</v>
+        <v>34.18784825</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1535708960549117</v>
+        <v>0.15498077172282</v>
       </c>
       <c r="T38">
-        <v>1.66718148671734</v>
+        <v>1.688991814905688</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.486362968395351</v>
+        <v>8.257001807087368</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1124841361853766</v>
+        <v>0.1122378988956097</v>
       </c>
       <c r="C39">
-        <v>206.5320920025045</v>
+        <v>204.6444300755522</v>
       </c>
       <c r="D39">
-        <v>295.2660920025045</v>
+        <v>296.3604300755521</v>
       </c>
       <c r="E39">
-        <v>-10.26600000000001</v>
+        <v>-7.283999999999992</v>
       </c>
       <c r="F39">
-        <v>110.334</v>
+        <v>113.316</v>
       </c>
       <c r="G39">
         <v>21.6</v>
@@ -4479,28 +4479,28 @@
         <v>48.74</v>
       </c>
       <c r="M39">
-        <v>5.902868999999999</v>
+        <v>6.062406</v>
       </c>
       <c r="N39">
-        <v>42.837131</v>
+        <v>42.677594</v>
       </c>
       <c r="O39">
-        <v>10.70928275</v>
+        <v>10.6693985</v>
       </c>
       <c r="P39">
-        <v>32.12784825</v>
+        <v>32.0081955</v>
       </c>
       <c r="Q39">
-        <v>34.18784825</v>
+        <v>34.0681955</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.15498077172282</v>
+        <v>0.1564361272509834</v>
       </c>
       <c r="T39">
-        <v>1.688991814905688</v>
+        <v>1.711505702067854</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.257001807087368</v>
+        <v>8.039712285848225</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1122378988956097</v>
+        <v>0.1119916616058429</v>
       </c>
       <c r="C40">
-        <v>204.6444300755522</v>
+        <v>202.76491016633</v>
       </c>
       <c r="D40">
-        <v>296.3604300755521</v>
+        <v>297.46291016633</v>
       </c>
       <c r="E40">
-        <v>-7.283999999999992</v>
+        <v>-4.301999999999992</v>
       </c>
       <c r="F40">
-        <v>113.316</v>
+        <v>116.298</v>
       </c>
       <c r="G40">
         <v>21.6</v>
@@ -4561,28 +4561,28 @@
         <v>48.74</v>
       </c>
       <c r="M40">
-        <v>6.062406</v>
+        <v>6.221943</v>
       </c>
       <c r="N40">
-        <v>42.677594</v>
+        <v>42.518057</v>
       </c>
       <c r="O40">
-        <v>10.6693985</v>
+        <v>10.62951425</v>
       </c>
       <c r="P40">
-        <v>32.0081955</v>
+        <v>31.88854275</v>
       </c>
       <c r="Q40">
-        <v>34.0681955</v>
+        <v>33.94854275</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1564361272509834</v>
+        <v>0.1579391993538408</v>
       </c>
       <c r="T40">
-        <v>1.711505702067854</v>
+        <v>1.734757749464845</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.039712285848225</v>
+        <v>7.833565816980323</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1119916616058429</v>
+        <v>0.111745424316076</v>
       </c>
       <c r="C41">
-        <v>202.76491016633</v>
+        <v>200.8936234806376</v>
       </c>
       <c r="D41">
-        <v>297.46291016633</v>
+        <v>298.5736234806375</v>
       </c>
       <c r="E41">
-        <v>-4.301999999999992</v>
+        <v>-1.319999999999993</v>
       </c>
       <c r="F41">
-        <v>116.298</v>
+        <v>119.28</v>
       </c>
       <c r="G41">
         <v>21.6</v>
@@ -4643,28 +4643,28 @@
         <v>48.74</v>
       </c>
       <c r="M41">
-        <v>6.221943</v>
+        <v>6.38148</v>
       </c>
       <c r="N41">
-        <v>42.518057</v>
+        <v>42.35852</v>
       </c>
       <c r="O41">
-        <v>10.62951425</v>
+        <v>10.58963</v>
       </c>
       <c r="P41">
-        <v>31.88854275</v>
+        <v>31.76889</v>
       </c>
       <c r="Q41">
-        <v>33.94854275</v>
+        <v>33.82889</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1579391993538408</v>
+        <v>0.1594923738601266</v>
       </c>
       <c r="T41">
-        <v>1.734757749464845</v>
+        <v>1.758784865108403</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.833565816980323</v>
+        <v>7.637726671555814</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.111745424316076</v>
+        <v>0.1117451870263091</v>
       </c>
       <c r="C42">
-        <v>200.8936234806376</v>
+        <v>197.9126978344867</v>
       </c>
       <c r="D42">
-        <v>298.5736234806375</v>
+        <v>298.5746978344866</v>
       </c>
       <c r="E42">
-        <v>-1.319999999999993</v>
+        <v>1.662000000000006</v>
       </c>
       <c r="F42">
-        <v>119.28</v>
+        <v>122.262</v>
       </c>
       <c r="G42">
         <v>21.6</v>
@@ -4725,45 +4725,45 @@
         <v>48.74</v>
       </c>
       <c r="M42">
-        <v>6.38148</v>
+        <v>6.6388266</v>
       </c>
       <c r="N42">
-        <v>42.35852</v>
+        <v>42.1011734</v>
       </c>
       <c r="O42">
-        <v>10.58963</v>
+        <v>10.52529335</v>
       </c>
       <c r="P42">
-        <v>31.76889</v>
+        <v>31.57588005</v>
       </c>
       <c r="Q42">
-        <v>33.82889</v>
+        <v>33.63588005</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1594923738601266</v>
+        <v>0.1610981983496765</v>
       </c>
       <c r="T42">
-        <v>1.758784865108403</v>
+        <v>1.783626459248352</v>
       </c>
       <c r="U42">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y42">
-        <v>7.637726671555814</v>
+        <v>7.3416588407355</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1117451870263091</v>
+        <v>0.1115049497365422</v>
       </c>
       <c r="C43">
-        <v>197.9126978344867</v>
+        <v>196.022377783841</v>
       </c>
       <c r="D43">
-        <v>298.5746978344866</v>
+        <v>299.666377783841</v>
       </c>
       <c r="E43">
-        <v>1.662000000000006</v>
+        <v>4.64400000000002</v>
       </c>
       <c r="F43">
-        <v>122.262</v>
+        <v>125.244</v>
       </c>
       <c r="G43">
         <v>21.6</v>
@@ -4807,28 +4807,28 @@
         <v>48.74</v>
       </c>
       <c r="M43">
-        <v>6.6388266</v>
+        <v>6.800749200000001</v>
       </c>
       <c r="N43">
-        <v>42.1011734</v>
+        <v>41.9392508</v>
       </c>
       <c r="O43">
-        <v>10.52529335</v>
+        <v>10.4848127</v>
       </c>
       <c r="P43">
-        <v>31.57588005</v>
+        <v>31.4544381</v>
       </c>
       <c r="Q43">
-        <v>33.63588005</v>
+        <v>33.51443810000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1610981983496765</v>
+        <v>0.1627593960974866</v>
       </c>
       <c r="T43">
-        <v>1.783626459248352</v>
+        <v>1.809324660082782</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.3416588407355</v>
+        <v>7.166857439765606</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1115049497365422</v>
+        <v>0.1112647124467754</v>
       </c>
       <c r="C44">
-        <v>196.022377783841</v>
+        <v>194.1400700568587</v>
       </c>
       <c r="D44">
-        <v>299.666377783841</v>
+        <v>300.7660700568587</v>
       </c>
       <c r="E44">
-        <v>4.643999999999991</v>
+        <v>7.626000000000005</v>
       </c>
       <c r="F44">
-        <v>125.244</v>
+        <v>128.226</v>
       </c>
       <c r="G44">
         <v>21.6</v>
@@ -4889,28 +4889,28 @@
         <v>48.74</v>
       </c>
       <c r="M44">
-        <v>6.800749199999999</v>
+        <v>6.9626718</v>
       </c>
       <c r="N44">
-        <v>41.9392508</v>
+        <v>41.7773282</v>
       </c>
       <c r="O44">
-        <v>10.4848127</v>
+        <v>10.44433205</v>
       </c>
       <c r="P44">
-        <v>31.4544381</v>
+        <v>31.33299615</v>
       </c>
       <c r="Q44">
-        <v>33.51443810000001</v>
+        <v>33.39299615</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1627593960974866</v>
+        <v>0.1644788814855708</v>
       </c>
       <c r="T44">
-        <v>1.809324660082782</v>
+        <v>1.83592455217456</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.166857439765608</v>
+        <v>7.000186336515244</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1112647124467754</v>
+        <v>0.1110244751570085</v>
       </c>
       <c r="C45">
-        <v>194.1400700568587</v>
+        <v>192.2658631874338</v>
       </c>
       <c r="D45">
-        <v>300.7660700568587</v>
+        <v>301.8738631874338</v>
       </c>
       <c r="E45">
-        <v>7.626000000000005</v>
+        <v>10.608</v>
       </c>
       <c r="F45">
-        <v>128.226</v>
+        <v>131.208</v>
       </c>
       <c r="G45">
         <v>21.6</v>
@@ -4971,28 +4971,28 @@
         <v>48.74</v>
       </c>
       <c r="M45">
-        <v>6.9626718</v>
+        <v>7.1245944</v>
       </c>
       <c r="N45">
-        <v>41.7773282</v>
+        <v>41.6154056</v>
       </c>
       <c r="O45">
-        <v>10.44433205</v>
+        <v>10.4038514</v>
       </c>
       <c r="P45">
-        <v>31.33299615</v>
+        <v>31.2115542</v>
       </c>
       <c r="Q45">
-        <v>33.39299615</v>
+        <v>33.2715542</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1644788814855708</v>
+        <v>0.1662597770660866</v>
       </c>
       <c r="T45">
-        <v>1.83592455217456</v>
+        <v>1.863474440412474</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.000186336515244</v>
+        <v>6.841091192503534</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1110244751570085</v>
+        <v>0.1107842378672416</v>
       </c>
       <c r="C46">
-        <v>192.2658631874338</v>
+        <v>190.3998470186478</v>
       </c>
       <c r="D46">
-        <v>301.8738631874338</v>
+        <v>302.9898470186478</v>
       </c>
       <c r="E46">
-        <v>10.608</v>
+        <v>13.59</v>
       </c>
       <c r="F46">
-        <v>131.208</v>
+        <v>134.19</v>
       </c>
       <c r="G46">
         <v>21.6</v>
@@ -5053,28 +5053,28 @@
         <v>48.74</v>
       </c>
       <c r="M46">
-        <v>7.1245944</v>
+        <v>7.286517</v>
       </c>
       <c r="N46">
-        <v>41.6154056</v>
+        <v>41.45348300000001</v>
       </c>
       <c r="O46">
-        <v>10.4038514</v>
+        <v>10.36337075</v>
       </c>
       <c r="P46">
-        <v>31.2115542</v>
+        <v>31.09011225</v>
       </c>
       <c r="Q46">
-        <v>33.2715542</v>
+        <v>33.15011225000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1662597770660866</v>
+        <v>0.1681054324858938</v>
       </c>
       <c r="T46">
-        <v>1.863474440412474</v>
+        <v>1.89202614276813</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.841091192503534</v>
+        <v>6.689066943781234</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1107842378672416</v>
+        <v>0.1105440005774747</v>
       </c>
       <c r="C47">
-        <v>190.3998470186478</v>
+        <v>188.5421127270596</v>
       </c>
       <c r="D47">
-        <v>302.9898470186478</v>
+        <v>304.1141127270595</v>
       </c>
       <c r="E47">
-        <v>13.59</v>
+        <v>16.572</v>
       </c>
       <c r="F47">
-        <v>134.19</v>
+        <v>137.172</v>
       </c>
       <c r="G47">
         <v>21.6</v>
@@ -5135,28 +5135,28 @@
         <v>48.74</v>
       </c>
       <c r="M47">
-        <v>7.286517</v>
+        <v>7.4484396</v>
       </c>
       <c r="N47">
-        <v>41.45348300000001</v>
+        <v>41.2915604</v>
       </c>
       <c r="O47">
-        <v>10.36337075</v>
+        <v>10.3228901</v>
       </c>
       <c r="P47">
-        <v>31.09011225</v>
+        <v>30.9686703</v>
       </c>
       <c r="Q47">
-        <v>33.15011225000001</v>
+        <v>33.0286703</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1681054324858938</v>
+        <v>0.170019445513842</v>
       </c>
       <c r="T47">
-        <v>1.89202614276813</v>
+        <v>1.921635315581403</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.689066943781234</v>
+        <v>6.543652445003381</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1105440005774747</v>
+        <v>0.1103037632877078</v>
       </c>
       <c r="C48">
-        <v>188.5421127270596</v>
+        <v>186.6927528475364</v>
       </c>
       <c r="D48">
-        <v>304.1141127270595</v>
+        <v>305.2467528475364</v>
       </c>
       <c r="E48">
-        <v>16.572</v>
+        <v>19.554</v>
       </c>
       <c r="F48">
-        <v>137.172</v>
+        <v>140.154</v>
       </c>
       <c r="G48">
         <v>21.6</v>
@@ -5217,28 +5217,28 @@
         <v>48.74</v>
       </c>
       <c r="M48">
-        <v>7.4484396</v>
+        <v>7.6103622</v>
       </c>
       <c r="N48">
-        <v>41.2915604</v>
+        <v>41.1296378</v>
       </c>
       <c r="O48">
-        <v>10.3228901</v>
+        <v>10.28240945</v>
       </c>
       <c r="P48">
-        <v>30.9686703</v>
+        <v>30.84722835</v>
       </c>
       <c r="Q48">
-        <v>33.0286703</v>
+        <v>32.90722835</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.170019445513842</v>
+        <v>0.1720056854485054</v>
       </c>
       <c r="T48">
-        <v>1.921635315581403</v>
+        <v>1.952361815670648</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.543652445003381</v>
+        <v>6.404425797237352</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1103037632877078</v>
+        <v>0.110063525997941</v>
       </c>
       <c r="C49">
-        <v>186.6927528475364</v>
+        <v>184.8518612986442</v>
       </c>
       <c r="D49">
-        <v>305.2467528475364</v>
+        <v>306.3878612986442</v>
       </c>
       <c r="E49">
-        <v>19.554</v>
+        <v>22.536</v>
       </c>
       <c r="F49">
-        <v>140.154</v>
+        <v>143.136</v>
       </c>
       <c r="G49">
         <v>21.6</v>
@@ -5299,28 +5299,28 @@
         <v>48.74</v>
       </c>
       <c r="M49">
-        <v>7.6103622</v>
+        <v>7.7722848</v>
       </c>
       <c r="N49">
-        <v>41.1296378</v>
+        <v>40.9677152</v>
       </c>
       <c r="O49">
-        <v>10.28240945</v>
+        <v>10.2419288</v>
       </c>
       <c r="P49">
-        <v>30.84722835</v>
+        <v>30.7257864</v>
       </c>
       <c r="Q49">
-        <v>32.90722835</v>
+        <v>32.7857864</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1720056854485054</v>
+        <v>0.1740683192268095</v>
       </c>
       <c r="T49">
-        <v>1.952361815670648</v>
+        <v>1.984270104224864</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.404425797237352</v>
+        <v>6.271000259794906</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.110063525997941</v>
+        <v>0.1098232887081741</v>
       </c>
       <c r="C50">
-        <v>184.8518612986442</v>
+        <v>183.0195334086066</v>
       </c>
       <c r="D50">
-        <v>306.3878612986442</v>
+        <v>307.5375334086066</v>
       </c>
       <c r="E50">
-        <v>22.536</v>
+        <v>25.518</v>
       </c>
       <c r="F50">
-        <v>143.136</v>
+        <v>146.118</v>
       </c>
       <c r="G50">
         <v>21.6</v>
@@ -5381,28 +5381,28 @@
         <v>48.74</v>
       </c>
       <c r="M50">
-        <v>7.7722848</v>
+        <v>7.9342074</v>
       </c>
       <c r="N50">
-        <v>40.9677152</v>
+        <v>40.8057926</v>
       </c>
       <c r="O50">
-        <v>10.2419288</v>
+        <v>10.20144815</v>
       </c>
       <c r="P50">
-        <v>30.7257864</v>
+        <v>30.60434445</v>
       </c>
       <c r="Q50">
-        <v>32.7857864</v>
+        <v>32.66434445</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1740683192268095</v>
+        <v>0.1762118406042629</v>
       </c>
       <c r="T50">
-        <v>1.984270104224864</v>
+        <v>2.017429698212579</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.271000259794906</v>
+        <v>6.143020662656235</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1098232887081741</v>
+        <v>0.1099580514184072</v>
       </c>
       <c r="C51">
-        <v>183.0195334086066</v>
+        <v>179.3915569398035</v>
       </c>
       <c r="D51">
-        <v>307.5375334086066</v>
+        <v>306.8915569398035</v>
       </c>
       <c r="E51">
-        <v>25.518</v>
+        <v>28.5</v>
       </c>
       <c r="F51">
-        <v>146.118</v>
+        <v>149.1</v>
       </c>
       <c r="G51">
         <v>21.6</v>
@@ -5463,45 +5463,45 @@
         <v>48.74</v>
       </c>
       <c r="M51">
-        <v>7.9342074</v>
+        <v>8.245229999999999</v>
       </c>
       <c r="N51">
-        <v>40.8057926</v>
+        <v>40.49477</v>
       </c>
       <c r="O51">
-        <v>10.20144815</v>
+        <v>10.1236925</v>
       </c>
       <c r="P51">
-        <v>30.60434445</v>
+        <v>30.3710775</v>
       </c>
       <c r="Q51">
-        <v>32.66434445</v>
+        <v>32.4310775</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1762118406042629</v>
+        <v>0.1784411028368144</v>
       </c>
       <c r="T51">
-        <v>2.017429698212579</v>
+        <v>2.051915675959803</v>
       </c>
       <c r="U51">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>6.143020662656235</v>
+        <v>5.911296592090215</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1099580514184072</v>
+        <v>0.1097253141286403</v>
       </c>
       <c r="C52">
-        <v>179.3915569398035</v>
+        <v>177.5268781479679</v>
       </c>
       <c r="D52">
-        <v>306.8915569398035</v>
+        <v>308.0088781479679</v>
       </c>
       <c r="E52">
-        <v>28.5</v>
+        <v>31.482</v>
       </c>
       <c r="F52">
-        <v>149.1</v>
+        <v>152.082</v>
       </c>
       <c r="G52">
         <v>21.6</v>
@@ -5545,28 +5545,28 @@
         <v>48.74</v>
       </c>
       <c r="M52">
-        <v>8.245229999999999</v>
+        <v>8.410134599999999</v>
       </c>
       <c r="N52">
-        <v>40.49477</v>
+        <v>40.3298654</v>
       </c>
       <c r="O52">
-        <v>10.1236925</v>
+        <v>10.08246635</v>
       </c>
       <c r="P52">
-        <v>30.3710775</v>
+        <v>30.24739905</v>
       </c>
       <c r="Q52">
-        <v>32.4310775</v>
+        <v>32.30739905</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1784411028368144</v>
+        <v>0.1807613553645721</v>
       </c>
       <c r="T52">
-        <v>2.051915675959803</v>
+        <v>2.087809244635485</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.911296592090215</v>
+        <v>5.795388815774721</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1097253141286403</v>
+        <v>0.1094925768388735</v>
       </c>
       <c r="C53">
-        <v>177.5268781479679</v>
+        <v>175.670364901403</v>
       </c>
       <c r="D53">
-        <v>308.0088781479679</v>
+        <v>309.1343649014029</v>
       </c>
       <c r="E53">
-        <v>31.482</v>
+        <v>34.464</v>
       </c>
       <c r="F53">
-        <v>152.082</v>
+        <v>155.064</v>
       </c>
       <c r="G53">
         <v>21.6</v>
@@ -5627,28 +5627,28 @@
         <v>48.74</v>
       </c>
       <c r="M53">
-        <v>8.410134599999999</v>
+        <v>8.575039199999999</v>
       </c>
       <c r="N53">
-        <v>40.3298654</v>
+        <v>40.1649608</v>
       </c>
       <c r="O53">
-        <v>10.08246635</v>
+        <v>10.0412402</v>
       </c>
       <c r="P53">
-        <v>30.24739905</v>
+        <v>30.1237206</v>
       </c>
       <c r="Q53">
-        <v>32.30739905</v>
+        <v>32.1837206</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1807613553645721</v>
+        <v>0.1831782850809864</v>
       </c>
       <c r="T53">
-        <v>2.087809244635485</v>
+        <v>2.125198378672653</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.795388815774721</v>
+        <v>5.683939030855976</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1094925768388735</v>
+        <v>0.1092598395491066</v>
       </c>
       <c r="C54">
-        <v>175.670364901403</v>
+        <v>173.822107040875</v>
       </c>
       <c r="D54">
-        <v>309.1343649014029</v>
+        <v>310.268107040875</v>
       </c>
       <c r="E54">
-        <v>34.464</v>
+        <v>37.446</v>
       </c>
       <c r="F54">
-        <v>155.064</v>
+        <v>158.046</v>
       </c>
       <c r="G54">
         <v>21.6</v>
@@ -5709,28 +5709,28 @@
         <v>48.74</v>
       </c>
       <c r="M54">
-        <v>8.575039199999999</v>
+        <v>8.739943800000001</v>
       </c>
       <c r="N54">
-        <v>40.1649608</v>
+        <v>40.0000562</v>
       </c>
       <c r="O54">
-        <v>10.0412402</v>
+        <v>10.00001405</v>
       </c>
       <c r="P54">
-        <v>30.1237206</v>
+        <v>30.00004215</v>
       </c>
       <c r="Q54">
-        <v>32.1837206</v>
+        <v>32.06004215</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1831782850809864</v>
+        <v>0.1856980628704395</v>
       </c>
       <c r="T54">
-        <v>2.125198378672653</v>
+        <v>2.164178539690127</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.683939030855976</v>
+        <v>5.576694898198316</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1092598395491066</v>
+        <v>0.1090271022593397</v>
       </c>
       <c r="C55">
-        <v>173.822107040875</v>
+        <v>171.9821957299565</v>
       </c>
       <c r="D55">
-        <v>310.268107040875</v>
+        <v>311.4101957299565</v>
       </c>
       <c r="E55">
-        <v>37.446</v>
+        <v>40.428</v>
       </c>
       <c r="F55">
-        <v>158.046</v>
+        <v>161.028</v>
       </c>
       <c r="G55">
         <v>21.6</v>
@@ -5791,28 +5791,28 @@
         <v>48.74</v>
       </c>
       <c r="M55">
-        <v>8.739943800000001</v>
+        <v>8.904848400000001</v>
       </c>
       <c r="N55">
-        <v>40.0000562</v>
+        <v>39.8351516</v>
       </c>
       <c r="O55">
-        <v>10.00001405</v>
+        <v>9.958787900000001</v>
       </c>
       <c r="P55">
-        <v>30.00004215</v>
+        <v>29.8763637</v>
       </c>
       <c r="Q55">
-        <v>32.06004215</v>
+        <v>31.9363637</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1856980628704395</v>
+        <v>0.1883273962159559</v>
       </c>
       <c r="T55">
-        <v>2.164178539690127</v>
+        <v>2.204853490317055</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.576694898198316</v>
+        <v>5.473422770453903</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1090271022593397</v>
+        <v>0.1087943649695728</v>
       </c>
       <c r="C56">
-        <v>171.9821957299565</v>
+        <v>170.1507234794619</v>
       </c>
       <c r="D56">
-        <v>311.4101957299565</v>
+        <v>312.5607234794619</v>
       </c>
       <c r="E56">
-        <v>40.428</v>
+        <v>43.41000000000003</v>
       </c>
       <c r="F56">
-        <v>161.028</v>
+        <v>164.01</v>
       </c>
       <c r="G56">
         <v>21.6</v>
@@ -5873,28 +5873,28 @@
         <v>48.74</v>
       </c>
       <c r="M56">
-        <v>8.904848400000001</v>
+        <v>9.069753000000002</v>
       </c>
       <c r="N56">
-        <v>39.8351516</v>
+        <v>39.670247</v>
       </c>
       <c r="O56">
-        <v>9.958787900000001</v>
+        <v>9.917561750000001</v>
       </c>
       <c r="P56">
-        <v>29.8763637</v>
+        <v>29.75268525</v>
       </c>
       <c r="Q56">
-        <v>31.9363637</v>
+        <v>31.81268525</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1883273962159559</v>
+        <v>0.1910735888212729</v>
       </c>
       <c r="T56">
-        <v>2.204853490317055</v>
+        <v>2.247336216527403</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.473422770453903</v>
+        <v>5.373905992809285</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1087943649695728</v>
+        <v>0.1085616276798059</v>
       </c>
       <c r="C57">
-        <v>170.1507234794619</v>
+        <v>168.3277841724272</v>
       </c>
       <c r="D57">
-        <v>312.5607234794619</v>
+        <v>313.7197841724272</v>
       </c>
       <c r="E57">
-        <v>43.41000000000003</v>
+        <v>46.39200000000002</v>
       </c>
       <c r="F57">
-        <v>164.01</v>
+        <v>166.992</v>
       </c>
       <c r="G57">
         <v>21.6</v>
@@ -5955,28 +5955,28 @@
         <v>48.74</v>
       </c>
       <c r="M57">
-        <v>9.069753000000002</v>
+        <v>9.234657600000002</v>
       </c>
       <c r="N57">
-        <v>39.670247</v>
+        <v>39.5053424</v>
       </c>
       <c r="O57">
-        <v>9.917561750000001</v>
+        <v>9.876335600000001</v>
       </c>
       <c r="P57">
-        <v>29.75268525</v>
+        <v>29.6290068</v>
       </c>
       <c r="Q57">
-        <v>31.81268525</v>
+        <v>31.6890068</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1910735888212729</v>
+        <v>0.1939446083631953</v>
       </c>
       <c r="T57">
-        <v>2.247336216527403</v>
+        <v>2.291749975747313</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.373905992809285</v>
+        <v>5.277943385794834</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1085616276798059</v>
+        <v>0.1083288903900391</v>
       </c>
       <c r="C58">
-        <v>168.3277841724272</v>
+        <v>166.5134730896476</v>
       </c>
       <c r="D58">
-        <v>313.7197841724272</v>
+        <v>314.8874730896476</v>
       </c>
       <c r="E58">
-        <v>46.39200000000002</v>
+        <v>49.37400000000002</v>
       </c>
       <c r="F58">
-        <v>166.992</v>
+        <v>169.974</v>
       </c>
       <c r="G58">
         <v>21.6</v>
@@ -6037,28 +6037,28 @@
         <v>48.74</v>
       </c>
       <c r="M58">
-        <v>9.234657600000002</v>
+        <v>9.399562200000002</v>
       </c>
       <c r="N58">
-        <v>39.5053424</v>
+        <v>39.3404378</v>
       </c>
       <c r="O58">
-        <v>9.876335600000001</v>
+        <v>9.835109450000001</v>
       </c>
       <c r="P58">
-        <v>29.6290068</v>
+        <v>29.50532835</v>
       </c>
       <c r="Q58">
-        <v>31.6890068</v>
+        <v>31.56532835</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1939446083631953</v>
+        <v>0.1969491636977653</v>
       </c>
       <c r="T58">
-        <v>2.291749975747313</v>
+        <v>2.338229491210008</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.277943385794834</v>
+        <v>5.185347887798433</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1083288903900391</v>
+        <v>0.1080961531002722</v>
       </c>
       <c r="C59">
-        <v>166.5134730896476</v>
+        <v>164.7078869357878</v>
       </c>
       <c r="D59">
-        <v>314.8874730896476</v>
+        <v>316.0638869357878</v>
       </c>
       <c r="E59">
-        <v>49.37400000000002</v>
+        <v>52.35600000000002</v>
       </c>
       <c r="F59">
-        <v>169.974</v>
+        <v>172.956</v>
       </c>
       <c r="G59">
         <v>21.6</v>
@@ -6119,28 +6119,28 @@
         <v>48.74</v>
       </c>
       <c r="M59">
-        <v>9.399562200000002</v>
+        <v>9.564466800000002</v>
       </c>
       <c r="N59">
-        <v>39.3404378</v>
+        <v>39.1755332</v>
       </c>
       <c r="O59">
-        <v>9.835109450000001</v>
+        <v>9.793883300000001</v>
       </c>
       <c r="P59">
-        <v>29.50532835</v>
+        <v>29.3816499</v>
       </c>
       <c r="Q59">
-        <v>31.56532835</v>
+        <v>31.4416499</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1969491636977653</v>
+        <v>0.2000967930958862</v>
       </c>
       <c r="T59">
-        <v>2.338229491210008</v>
+        <v>2.386922316932832</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.185347887798433</v>
+        <v>5.095945338008805</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1080961531002722</v>
+        <v>0.1078634158105053</v>
       </c>
       <c r="C60">
-        <v>164.7078869357878</v>
+        <v>162.9111238660788</v>
       </c>
       <c r="D60">
-        <v>316.0638869357878</v>
+        <v>317.2491238660787</v>
       </c>
       <c r="E60">
-        <v>52.35599999999999</v>
+        <v>55.33799999999999</v>
       </c>
       <c r="F60">
-        <v>172.956</v>
+        <v>175.938</v>
       </c>
       <c r="G60">
         <v>21.6</v>
@@ -6201,28 +6201,28 @@
         <v>48.74</v>
       </c>
       <c r="M60">
-        <v>9.5644668</v>
+        <v>9.7293714</v>
       </c>
       <c r="N60">
-        <v>39.1755332</v>
+        <v>39.0106286</v>
       </c>
       <c r="O60">
-        <v>9.793883300000001</v>
+        <v>9.752657150000001</v>
       </c>
       <c r="P60">
-        <v>29.3816499</v>
+        <v>29.25797145</v>
       </c>
       <c r="Q60">
-        <v>31.4416499</v>
+        <v>31.31797145</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2000967930958861</v>
+        <v>0.2033979653914764</v>
       </c>
       <c r="T60">
-        <v>2.386922316932832</v>
+        <v>2.437990402447013</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.095945338008806</v>
+        <v>5.009573383127301</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1078634158105053</v>
+        <v>0.1076306785207384</v>
       </c>
       <c r="C61">
-        <v>162.9111238660788</v>
+        <v>161.1232835136192</v>
       </c>
       <c r="D61">
-        <v>317.2491238660787</v>
+        <v>318.4432835136191</v>
       </c>
       <c r="E61">
-        <v>55.33799999999999</v>
+        <v>58.31999999999999</v>
       </c>
       <c r="F61">
-        <v>175.938</v>
+        <v>178.92</v>
       </c>
       <c r="G61">
         <v>21.6</v>
@@ -6283,28 +6283,28 @@
         <v>48.74</v>
       </c>
       <c r="M61">
-        <v>9.7293714</v>
+        <v>9.894276</v>
       </c>
       <c r="N61">
-        <v>39.0106286</v>
+        <v>38.845724</v>
       </c>
       <c r="O61">
-        <v>9.752657150000001</v>
+        <v>9.711431000000001</v>
       </c>
       <c r="P61">
-        <v>29.25797145</v>
+        <v>29.134293</v>
       </c>
       <c r="Q61">
-        <v>31.31797145</v>
+        <v>31.194293</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2033979653914764</v>
+        <v>0.2068641963018461</v>
       </c>
       <c r="T61">
-        <v>2.437990402447013</v>
+        <v>2.491611892236904</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.009573383127301</v>
+        <v>4.926080493408513</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1076306785207384</v>
+        <v>0.1073979412309716</v>
       </c>
       <c r="C62">
-        <v>161.1232835136192</v>
+        <v>159.3444670172938</v>
       </c>
       <c r="D62">
-        <v>318.4432835136191</v>
+        <v>319.6464670172937</v>
       </c>
       <c r="E62">
-        <v>58.31999999999999</v>
+        <v>61.30199999999999</v>
       </c>
       <c r="F62">
-        <v>178.92</v>
+        <v>181.902</v>
       </c>
       <c r="G62">
         <v>21.6</v>
@@ -6365,28 +6365,28 @@
         <v>48.74</v>
       </c>
       <c r="M62">
-        <v>9.894276</v>
+        <v>10.0591806</v>
       </c>
       <c r="N62">
-        <v>38.845724</v>
+        <v>38.6808194</v>
       </c>
       <c r="O62">
-        <v>9.711431000000001</v>
+        <v>9.670204850000001</v>
       </c>
       <c r="P62">
-        <v>29.134293</v>
+        <v>29.01061455</v>
       </c>
       <c r="Q62">
-        <v>31.194293</v>
+        <v>31.07061455</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2068641963018461</v>
+        <v>0.2105081826435168</v>
       </c>
       <c r="T62">
-        <v>2.491611892236904</v>
+        <v>2.547983202016019</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.926080493408513</v>
+        <v>4.845325075483784</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1073979412309716</v>
+        <v>0.1071652039412047</v>
       </c>
       <c r="C63">
-        <v>159.3444670172938</v>
+        <v>157.5747770503288</v>
       </c>
       <c r="D63">
-        <v>319.6464670172937</v>
+        <v>320.8587770503288</v>
       </c>
       <c r="E63">
-        <v>61.30199999999999</v>
+        <v>64.28399999999999</v>
       </c>
       <c r="F63">
-        <v>181.902</v>
+        <v>184.884</v>
       </c>
       <c r="G63">
         <v>21.6</v>
@@ -6447,28 +6447,28 @@
         <v>48.74</v>
       </c>
       <c r="M63">
-        <v>10.0591806</v>
+        <v>10.2240852</v>
       </c>
       <c r="N63">
-        <v>38.6808194</v>
+        <v>38.5159148</v>
       </c>
       <c r="O63">
-        <v>9.670204850000001</v>
+        <v>9.628978700000001</v>
       </c>
       <c r="P63">
-        <v>29.01061455</v>
+        <v>28.8869361</v>
       </c>
       <c r="Q63">
-        <v>31.07061455</v>
+        <v>30.9469361</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2105081826435168</v>
+        <v>0.2143439577400123</v>
       </c>
       <c r="T63">
-        <v>2.547983202016019</v>
+        <v>2.607321422836141</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.845325075483784</v>
+        <v>4.767174671040497</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1071652039412047</v>
+        <v>0.1069324666514378</v>
       </c>
       <c r="C64">
-        <v>157.5747770503288</v>
+        <v>155.8143178494985</v>
       </c>
       <c r="D64">
-        <v>320.8587770503288</v>
+        <v>322.0803178494984</v>
       </c>
       <c r="E64">
-        <v>64.28399999999999</v>
+        <v>67.26599999999999</v>
       </c>
       <c r="F64">
-        <v>184.884</v>
+        <v>187.866</v>
       </c>
       <c r="G64">
         <v>21.6</v>
@@ -6529,28 +6529,28 @@
         <v>48.74</v>
       </c>
       <c r="M64">
-        <v>10.2240852</v>
+        <v>10.3889898</v>
       </c>
       <c r="N64">
-        <v>38.5159148</v>
+        <v>38.3510102</v>
       </c>
       <c r="O64">
-        <v>9.628978700000001</v>
+        <v>9.587752550000001</v>
       </c>
       <c r="P64">
-        <v>28.8869361</v>
+        <v>28.76325765</v>
       </c>
       <c r="Q64">
-        <v>30.9469361</v>
+        <v>30.82325765</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2143439577400123</v>
+        <v>0.218387072030913</v>
       </c>
       <c r="T64">
-        <v>2.607321422836141</v>
+        <v>2.669867115051944</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.767174671040497</v>
+        <v>4.691505231817631</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1069324666514378</v>
+        <v>0.1066997293616709</v>
       </c>
       <c r="C65">
-        <v>155.8143178494985</v>
+        <v>154.0631952450018</v>
       </c>
       <c r="D65">
-        <v>322.0803178494984</v>
+        <v>323.3111952450017</v>
       </c>
       <c r="E65">
-        <v>67.26599999999999</v>
+        <v>70.24799999999999</v>
       </c>
       <c r="F65">
-        <v>187.866</v>
+        <v>190.848</v>
       </c>
       <c r="G65">
         <v>21.6</v>
@@ -6611,28 +6611,28 @@
         <v>48.74</v>
       </c>
       <c r="M65">
-        <v>10.3889898</v>
+        <v>10.5538944</v>
       </c>
       <c r="N65">
-        <v>38.3510102</v>
+        <v>38.1861056</v>
       </c>
       <c r="O65">
-        <v>9.587752550000001</v>
+        <v>9.546526400000001</v>
       </c>
       <c r="P65">
-        <v>28.76325765</v>
+        <v>28.6395792</v>
       </c>
       <c r="Q65">
-        <v>30.82325765</v>
+        <v>30.6995792</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.218387072030913</v>
+        <v>0.2226548037824192</v>
       </c>
       <c r="T65">
-        <v>2.669867115051944</v>
+        <v>2.735887567946404</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.691505231817631</v>
+        <v>4.618200462570481</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1066997293616709</v>
+        <v>0.106466992071904</v>
       </c>
       <c r="C66">
-        <v>154.0631952450018</v>
+        <v>152.3215166910267</v>
       </c>
       <c r="D66">
-        <v>323.3111952450017</v>
+        <v>324.5515166910267</v>
       </c>
       <c r="E66">
-        <v>70.24799999999999</v>
+        <v>73.23000000000002</v>
       </c>
       <c r="F66">
-        <v>190.848</v>
+        <v>193.83</v>
       </c>
       <c r="G66">
         <v>21.6</v>
@@ -6693,28 +6693,28 @@
         <v>48.74</v>
       </c>
       <c r="M66">
-        <v>10.5538944</v>
+        <v>10.718799</v>
       </c>
       <c r="N66">
-        <v>38.1861056</v>
+        <v>38.021201</v>
       </c>
       <c r="O66">
-        <v>9.546526400000001</v>
+        <v>9.505300250000001</v>
       </c>
       <c r="P66">
-        <v>28.6395792</v>
+        <v>28.51590075</v>
       </c>
       <c r="Q66">
-        <v>30.6995792</v>
+        <v>30.57590075</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2226548037824192</v>
+        <v>0.2271664059197259</v>
       </c>
       <c r="T66">
-        <v>2.735887567946404</v>
+        <v>2.805680618149119</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.618200462570481</v>
+        <v>4.547151224684781</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.106466992071904</v>
+        <v>0.1074717547821371</v>
       </c>
       <c r="C67">
-        <v>152.3215166910267</v>
+        <v>144.0518892727261</v>
       </c>
       <c r="D67">
-        <v>324.5515166910267</v>
+        <v>319.2638892727261</v>
       </c>
       <c r="E67">
-        <v>73.23000000000002</v>
+        <v>76.21200000000002</v>
       </c>
       <c r="F67">
-        <v>193.83</v>
+        <v>196.812</v>
       </c>
       <c r="G67">
         <v>21.6</v>
@@ -6775,45 +6775,45 @@
         <v>48.74</v>
       </c>
       <c r="M67">
-        <v>10.718799</v>
+        <v>11.3757336</v>
       </c>
       <c r="N67">
-        <v>38.021201</v>
+        <v>37.3642664</v>
       </c>
       <c r="O67">
-        <v>9.505300250000001</v>
+        <v>9.3410666</v>
       </c>
       <c r="P67">
-        <v>28.51590075</v>
+        <v>28.0231998</v>
       </c>
       <c r="Q67">
-        <v>30.57590075</v>
+        <v>30.0831998</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2271664059197259</v>
+        <v>0.2319433964180505</v>
       </c>
       <c r="T67">
-        <v>2.805680618149119</v>
+        <v>2.879579141893169</v>
       </c>
       <c r="U67">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V67">
         <v>0.25</v>
       </c>
       <c r="W67">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>4.547151224684781</v>
+        <v>4.284558843747887</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1074717547821371</v>
+        <v>0.1072577674923703</v>
       </c>
       <c r="C68">
-        <v>144.0518892727261</v>
+        <v>142.1815211652185</v>
       </c>
       <c r="D68">
-        <v>319.2638892727261</v>
+        <v>320.3755211652185</v>
       </c>
       <c r="E68">
-        <v>76.21200000000002</v>
+        <v>79.19400000000002</v>
       </c>
       <c r="F68">
-        <v>196.812</v>
+        <v>199.794</v>
       </c>
       <c r="G68">
         <v>21.6</v>
@@ -6857,28 +6857,28 @@
         <v>48.74</v>
       </c>
       <c r="M68">
-        <v>11.3757336</v>
+        <v>11.5480932</v>
       </c>
       <c r="N68">
-        <v>37.3642664</v>
+        <v>37.1919068</v>
       </c>
       <c r="O68">
-        <v>9.3410666</v>
+        <v>9.2979767</v>
       </c>
       <c r="P68">
-        <v>28.0231998</v>
+        <v>27.8939301</v>
       </c>
       <c r="Q68">
-        <v>30.0831998</v>
+        <v>29.9539301</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2319433964180505</v>
+        <v>0.2370099014920312</v>
       </c>
       <c r="T68">
-        <v>2.879579141893169</v>
+        <v>2.95795636404595</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.284558843747887</v>
+        <v>4.220610204288963</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1072577674923703</v>
+        <v>0.1070437802026034</v>
       </c>
       <c r="C69">
-        <v>142.1815211652185</v>
+        <v>140.3189211966176</v>
       </c>
       <c r="D69">
-        <v>320.3755211652185</v>
+        <v>321.4949211966176</v>
       </c>
       <c r="E69">
-        <v>79.19400000000002</v>
+        <v>82.17600000000002</v>
       </c>
       <c r="F69">
-        <v>199.794</v>
+        <v>202.776</v>
       </c>
       <c r="G69">
         <v>21.6</v>
@@ -6939,28 +6939,28 @@
         <v>48.74</v>
       </c>
       <c r="M69">
-        <v>11.5480932</v>
+        <v>11.7204528</v>
       </c>
       <c r="N69">
-        <v>37.1919068</v>
+        <v>37.0195472</v>
       </c>
       <c r="O69">
-        <v>9.2979767</v>
+        <v>9.2548868</v>
       </c>
       <c r="P69">
-        <v>27.8939301</v>
+        <v>27.7646604</v>
       </c>
       <c r="Q69">
-        <v>29.9539301</v>
+        <v>29.8246604</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2370099014920312</v>
+        <v>0.2423930631331357</v>
       </c>
       <c r="T69">
-        <v>2.95795636404595</v>
+        <v>3.04123216258328</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.220610204288963</v>
+        <v>4.158542407167067</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1070437802026034</v>
+        <v>0.1068297929128365</v>
       </c>
       <c r="C70">
-        <v>140.3189211966176</v>
+        <v>138.4641710786372</v>
       </c>
       <c r="D70">
-        <v>321.4949211966176</v>
+        <v>322.6221710786372</v>
       </c>
       <c r="E70">
-        <v>82.17600000000002</v>
+        <v>85.15800000000002</v>
       </c>
       <c r="F70">
-        <v>202.776</v>
+        <v>205.758</v>
       </c>
       <c r="G70">
         <v>21.6</v>
@@ -7021,28 +7021,28 @@
         <v>48.74</v>
       </c>
       <c r="M70">
-        <v>11.7204528</v>
+        <v>11.8928124</v>
       </c>
       <c r="N70">
-        <v>37.0195472</v>
+        <v>36.8471876</v>
       </c>
       <c r="O70">
-        <v>9.2548868</v>
+        <v>9.2117969</v>
       </c>
       <c r="P70">
-        <v>27.7646604</v>
+        <v>27.6353907</v>
       </c>
       <c r="Q70">
-        <v>29.8246604</v>
+        <v>29.6953907</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2423930631331357</v>
+        <v>0.2481235255252792</v>
       </c>
       <c r="T70">
-        <v>3.04123216258328</v>
+        <v>3.129880593284308</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.158542407167067</v>
+        <v>4.098273676628414</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1068297929128365</v>
+        <v>0.1066158056230697</v>
       </c>
       <c r="C71">
-        <v>138.4641710786372</v>
+        <v>136.6173536730389</v>
       </c>
       <c r="D71">
-        <v>322.6221710786372</v>
+        <v>323.7573536730389</v>
       </c>
       <c r="E71">
-        <v>85.15800000000002</v>
+        <v>88.14000000000001</v>
       </c>
       <c r="F71">
-        <v>205.758</v>
+        <v>208.74</v>
       </c>
       <c r="G71">
         <v>21.6</v>
@@ -7103,28 +7103,28 @@
         <v>48.74</v>
       </c>
       <c r="M71">
-        <v>11.8928124</v>
+        <v>12.065172</v>
       </c>
       <c r="N71">
-        <v>36.8471876</v>
+        <v>36.674828</v>
       </c>
       <c r="O71">
-        <v>9.2117969</v>
+        <v>9.168706999999999</v>
       </c>
       <c r="P71">
-        <v>27.6353907</v>
+        <v>27.506121</v>
       </c>
       <c r="Q71">
-        <v>29.6953907</v>
+        <v>29.566121</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2481235255252792</v>
+        <v>0.2542360187435656</v>
       </c>
       <c r="T71">
-        <v>3.129880593284308</v>
+        <v>3.224438919365405</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.098273676628414</v>
+        <v>4.039726909819437</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1066158056230697</v>
+        <v>0.1082655683333028</v>
       </c>
       <c r="C72">
-        <v>136.6173536730389</v>
+        <v>125.0846781008009</v>
       </c>
       <c r="D72">
-        <v>323.7573536730389</v>
+        <v>315.2066781008008</v>
       </c>
       <c r="E72">
-        <v>88.14000000000001</v>
+        <v>91.12200000000001</v>
       </c>
       <c r="F72">
-        <v>208.74</v>
+        <v>211.722</v>
       </c>
       <c r="G72">
         <v>21.6</v>
@@ -7185,45 +7185,45 @@
         <v>48.74</v>
       </c>
       <c r="M72">
-        <v>12.065172</v>
+        <v>12.9785586</v>
       </c>
       <c r="N72">
-        <v>36.674828</v>
+        <v>35.7614414</v>
       </c>
       <c r="O72">
-        <v>9.168706999999999</v>
+        <v>8.940360350000001</v>
       </c>
       <c r="P72">
-        <v>27.506121</v>
+        <v>26.82108105</v>
       </c>
       <c r="Q72">
-        <v>29.566121</v>
+        <v>28.88108105</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2542360187435656</v>
+        <v>0.2607700632182855</v>
       </c>
       <c r="T72">
-        <v>3.224438919365405</v>
+        <v>3.325518509314164</v>
       </c>
       <c r="U72">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V72">
         <v>0.25</v>
       </c>
       <c r="W72">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y72">
-        <v>4.039726909819437</v>
+        <v>3.75542473568675</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1082655683333028</v>
+        <v>0.1080778310435359</v>
       </c>
       <c r="C73">
-        <v>125.0846781008009</v>
+        <v>123.0528725194489</v>
       </c>
       <c r="D73">
-        <v>315.2066781008008</v>
+        <v>316.1568725194489</v>
       </c>
       <c r="E73">
-        <v>91.12199999999999</v>
+        <v>94.10399999999998</v>
       </c>
       <c r="F73">
-        <v>211.722</v>
+        <v>214.704</v>
       </c>
       <c r="G73">
         <v>21.6</v>
@@ -7267,28 +7267,28 @@
         <v>48.74</v>
       </c>
       <c r="M73">
-        <v>12.9785586</v>
+        <v>13.1613552</v>
       </c>
       <c r="N73">
-        <v>35.7614414</v>
+        <v>35.57864480000001</v>
       </c>
       <c r="O73">
-        <v>8.940360350000001</v>
+        <v>8.894661200000002</v>
       </c>
       <c r="P73">
-        <v>26.82108105</v>
+        <v>26.6839836</v>
       </c>
       <c r="Q73">
-        <v>28.88108105</v>
+        <v>28.7439836</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2607700632182854</v>
+        <v>0.2677708251554853</v>
       </c>
       <c r="T73">
-        <v>3.325518509314163</v>
+        <v>3.433818069973547</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.755424735686751</v>
+        <v>3.703266058802213</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1080778310435359</v>
+        <v>0.107890093753769</v>
       </c>
       <c r="C74">
-        <v>123.0528725194489</v>
+        <v>121.0268130052751</v>
       </c>
       <c r="D74">
-        <v>316.1568725194489</v>
+        <v>317.1128130052751</v>
       </c>
       <c r="E74">
-        <v>94.10399999999998</v>
+        <v>97.08599999999998</v>
       </c>
       <c r="F74">
-        <v>214.704</v>
+        <v>217.686</v>
       </c>
       <c r="G74">
         <v>21.6</v>
@@ -7349,28 +7349,28 @@
         <v>48.74</v>
       </c>
       <c r="M74">
-        <v>13.1613552</v>
+        <v>13.3441518</v>
       </c>
       <c r="N74">
-        <v>35.57864480000001</v>
+        <v>35.3958482</v>
       </c>
       <c r="O74">
-        <v>8.894661200000002</v>
+        <v>8.848962050000001</v>
       </c>
       <c r="P74">
-        <v>26.6839836</v>
+        <v>26.54688615</v>
       </c>
       <c r="Q74">
-        <v>28.7439836</v>
+        <v>28.60688615</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2677708251554853</v>
+        <v>0.2752901620509963</v>
       </c>
       <c r="T74">
-        <v>3.433818069973547</v>
+        <v>3.550139820311405</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.703266058802213</v>
+        <v>3.652536386763826</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.107890093753769</v>
+        <v>0.1077023564640021</v>
       </c>
       <c r="C75">
-        <v>121.0268130052751</v>
+        <v>119.0065518382479</v>
       </c>
       <c r="D75">
-        <v>317.1128130052751</v>
+        <v>318.0745518382479</v>
       </c>
       <c r="E75">
-        <v>97.08599999999998</v>
+        <v>100.068</v>
       </c>
       <c r="F75">
-        <v>217.686</v>
+        <v>220.668</v>
       </c>
       <c r="G75">
         <v>21.6</v>
@@ -7431,28 +7431,28 @@
         <v>48.74</v>
       </c>
       <c r="M75">
-        <v>13.3441518</v>
+        <v>13.5269484</v>
       </c>
       <c r="N75">
-        <v>35.3958482</v>
+        <v>35.2130516</v>
       </c>
       <c r="O75">
-        <v>8.848962050000001</v>
+        <v>8.8032629</v>
       </c>
       <c r="P75">
-        <v>26.54688615</v>
+        <v>26.4097887</v>
       </c>
       <c r="Q75">
-        <v>28.60688615</v>
+        <v>28.4697887</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2752901620509963</v>
+        <v>0.2833879094769313</v>
       </c>
       <c r="T75">
-        <v>3.550139820311405</v>
+        <v>3.675409397598328</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.652536386763826</v>
+        <v>3.603177786942693</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1077023564640021</v>
+        <v>0.1075146191742353</v>
       </c>
       <c r="C76">
-        <v>119.0065518382479</v>
+        <v>116.9921419344832</v>
       </c>
       <c r="D76">
-        <v>318.0745518382479</v>
+        <v>319.0421419344832</v>
       </c>
       <c r="E76">
-        <v>100.068</v>
+        <v>103.05</v>
       </c>
       <c r="F76">
-        <v>220.668</v>
+        <v>223.65</v>
       </c>
       <c r="G76">
         <v>21.6</v>
@@ -7513,28 +7513,28 @@
         <v>48.74</v>
       </c>
       <c r="M76">
-        <v>13.5269484</v>
+        <v>13.709745</v>
       </c>
       <c r="N76">
-        <v>35.2130516</v>
+        <v>35.030255</v>
       </c>
       <c r="O76">
-        <v>8.8032629</v>
+        <v>8.757563750000001</v>
       </c>
       <c r="P76">
-        <v>26.4097887</v>
+        <v>26.27269125</v>
       </c>
       <c r="Q76">
-        <v>28.4697887</v>
+        <v>28.33269125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2833879094769313</v>
+        <v>0.2921334766969411</v>
       </c>
       <c r="T76">
-        <v>3.675409397598328</v>
+        <v>3.810700541068206</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.603177786942693</v>
+        <v>3.555135416450124</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1075146191742353</v>
+        <v>0.1073268818844684</v>
       </c>
       <c r="C77">
-        <v>116.9921419344832</v>
+        <v>114.9836368559498</v>
       </c>
       <c r="D77">
-        <v>319.0421419344832</v>
+        <v>320.0156368559498</v>
       </c>
       <c r="E77">
-        <v>103.05</v>
+        <v>106.032</v>
       </c>
       <c r="F77">
-        <v>223.65</v>
+        <v>226.632</v>
       </c>
       <c r="G77">
         <v>21.6</v>
@@ -7595,28 +7595,28 @@
         <v>48.74</v>
       </c>
       <c r="M77">
-        <v>13.709745</v>
+        <v>13.8925416</v>
       </c>
       <c r="N77">
-        <v>35.030255</v>
+        <v>34.8474584</v>
       </c>
       <c r="O77">
-        <v>8.757563750000001</v>
+        <v>8.7118646</v>
       </c>
       <c r="P77">
-        <v>26.27269125</v>
+        <v>26.1355938</v>
       </c>
       <c r="Q77">
-        <v>28.33269125</v>
+        <v>28.1955938</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2921334766969411</v>
+        <v>0.3016078411852849</v>
       </c>
       <c r="T77">
-        <v>3.810700541068206</v>
+        <v>3.957265946493906</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.555135416450124</v>
+        <v>3.508357318865253</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1073268818844684</v>
+        <v>0.1087561445947015</v>
       </c>
       <c r="C78">
-        <v>114.9836368559498</v>
+        <v>104.7364776027224</v>
       </c>
       <c r="D78">
-        <v>320.0156368559498</v>
+        <v>312.7504776027224</v>
       </c>
       <c r="E78">
-        <v>106.032</v>
+        <v>109.014</v>
       </c>
       <c r="F78">
-        <v>226.632</v>
+        <v>229.614</v>
       </c>
       <c r="G78">
         <v>21.6</v>
@@ -7677,45 +7677,45 @@
         <v>48.74</v>
       </c>
       <c r="M78">
-        <v>13.8925416</v>
+        <v>14.7182574</v>
       </c>
       <c r="N78">
-        <v>34.8474584</v>
+        <v>34.0217426</v>
       </c>
       <c r="O78">
-        <v>8.7118646</v>
+        <v>8.505435650000001</v>
       </c>
       <c r="P78">
-        <v>26.1355938</v>
+        <v>25.51630695</v>
       </c>
       <c r="Q78">
-        <v>28.1955938</v>
+        <v>27.57630695</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3016078411852849</v>
+        <v>0.311906063455224</v>
       </c>
       <c r="T78">
-        <v>3.957265946493906</v>
+        <v>4.116576169782711</v>
       </c>
       <c r="U78">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V78">
         <v>0.25</v>
       </c>
       <c r="W78">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y78">
-        <v>3.508357318865253</v>
+        <v>3.311533334102446</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1087561445947015</v>
+        <v>0.1085894073049346</v>
       </c>
       <c r="C79">
-        <v>104.7364776027224</v>
+        <v>102.5849865889839</v>
       </c>
       <c r="D79">
-        <v>312.7504776027224</v>
+        <v>313.5809865889839</v>
       </c>
       <c r="E79">
-        <v>109.014</v>
+        <v>111.996</v>
       </c>
       <c r="F79">
-        <v>229.614</v>
+        <v>232.596</v>
       </c>
       <c r="G79">
         <v>21.6</v>
@@ -7759,28 +7759,28 @@
         <v>48.74</v>
       </c>
       <c r="M79">
-        <v>14.7182574</v>
+        <v>14.9094036</v>
       </c>
       <c r="N79">
-        <v>34.0217426</v>
+        <v>33.8305964</v>
       </c>
       <c r="O79">
-        <v>8.505435650000001</v>
+        <v>8.457649100000001</v>
       </c>
       <c r="P79">
-        <v>25.51630695</v>
+        <v>25.3729473</v>
       </c>
       <c r="Q79">
-        <v>27.57630695</v>
+        <v>27.4329473</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.311906063455224</v>
+        <v>0.3231404877497028</v>
       </c>
       <c r="T79">
-        <v>4.116576169782711</v>
+        <v>4.290369140643224</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.311533334102446</v>
+        <v>3.26907777853703</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1085894073049346</v>
+        <v>0.1084226700151678</v>
       </c>
       <c r="C80">
-        <v>102.5849865889839</v>
+        <v>100.437918153122</v>
       </c>
       <c r="D80">
-        <v>313.5809865889839</v>
+        <v>314.415918153122</v>
       </c>
       <c r="E80">
-        <v>111.996</v>
+        <v>114.978</v>
       </c>
       <c r="F80">
-        <v>232.596</v>
+        <v>235.578</v>
       </c>
       <c r="G80">
         <v>21.6</v>
@@ -7841,28 +7841,28 @@
         <v>48.74</v>
       </c>
       <c r="M80">
-        <v>14.9094036</v>
+        <v>15.1005498</v>
       </c>
       <c r="N80">
-        <v>33.8305964</v>
+        <v>33.6394502</v>
       </c>
       <c r="O80">
-        <v>8.457649100000001</v>
+        <v>8.40986255</v>
       </c>
       <c r="P80">
-        <v>25.3729473</v>
+        <v>25.22958765</v>
       </c>
       <c r="Q80">
-        <v>27.4329473</v>
+        <v>27.28958765</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3231404877497028</v>
+        <v>0.3354448572150846</v>
       </c>
       <c r="T80">
-        <v>4.290369140643224</v>
+        <v>4.480713823014264</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.26907777853703</v>
+        <v>3.227697047163143</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1084226700151678</v>
+        <v>0.1082559327254009</v>
       </c>
       <c r="C81">
-        <v>100.437918153122</v>
+        <v>98.29530771572627</v>
       </c>
       <c r="D81">
-        <v>314.415918153122</v>
+        <v>315.2553077157262</v>
       </c>
       <c r="E81">
-        <v>114.978</v>
+        <v>117.96</v>
       </c>
       <c r="F81">
-        <v>235.578</v>
+        <v>238.56</v>
       </c>
       <c r="G81">
         <v>21.6</v>
@@ -7923,28 +7923,28 @@
         <v>48.74</v>
       </c>
       <c r="M81">
-        <v>15.1005498</v>
+        <v>15.291696</v>
       </c>
       <c r="N81">
-        <v>33.6394502</v>
+        <v>33.448304</v>
       </c>
       <c r="O81">
-        <v>8.40986255</v>
+        <v>8.362076</v>
       </c>
       <c r="P81">
-        <v>25.22958765</v>
+        <v>25.086228</v>
       </c>
       <c r="Q81">
-        <v>27.28958765</v>
+        <v>27.146228</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3354448572150846</v>
+        <v>0.3489796636270044</v>
       </c>
       <c r="T81">
-        <v>4.480713823014264</v>
+        <v>4.690092973622408</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.227697047163143</v>
+        <v>3.187350834073604</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1082559327254009</v>
+        <v>0.108089195435634</v>
       </c>
       <c r="C82">
-        <v>98.29530771572627</v>
+        <v>96.15719107664492</v>
       </c>
       <c r="D82">
-        <v>315.2553077157262</v>
+        <v>316.0991910766449</v>
       </c>
       <c r="E82">
-        <v>117.96</v>
+        <v>120.942</v>
       </c>
       <c r="F82">
-        <v>238.56</v>
+        <v>241.542</v>
       </c>
       <c r="G82">
         <v>21.6</v>
@@ -8005,28 +8005,28 @@
         <v>48.74</v>
       </c>
       <c r="M82">
-        <v>15.291696</v>
+        <v>15.4828422</v>
       </c>
       <c r="N82">
-        <v>33.448304</v>
+        <v>33.2571578</v>
       </c>
       <c r="O82">
-        <v>8.362076</v>
+        <v>8.31428945</v>
       </c>
       <c r="P82">
-        <v>25.086228</v>
+        <v>24.94286835</v>
       </c>
       <c r="Q82">
-        <v>27.146228</v>
+        <v>27.00286835</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3489796636270044</v>
+        <v>0.3639391865033369</v>
       </c>
       <c r="T82">
-        <v>4.690092973622408</v>
+        <v>4.921512034820882</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.187350834073604</v>
+        <v>3.1480008237764</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.108089195435634</v>
+        <v>0.1079224581458671</v>
       </c>
       <c r="C83">
-        <v>96.15719107664492</v>
+        <v>94.02360442007483</v>
       </c>
       <c r="D83">
-        <v>316.0991910766449</v>
+        <v>316.9476044200748</v>
       </c>
       <c r="E83">
-        <v>120.942</v>
+        <v>123.924</v>
       </c>
       <c r="F83">
-        <v>241.542</v>
+        <v>244.524</v>
       </c>
       <c r="G83">
         <v>21.6</v>
@@ -8087,28 +8087,28 @@
         <v>48.74</v>
       </c>
       <c r="M83">
-        <v>15.4828422</v>
+        <v>15.6739884</v>
       </c>
       <c r="N83">
-        <v>33.2571578</v>
+        <v>33.0660116</v>
       </c>
       <c r="O83">
-        <v>8.31428945</v>
+        <v>8.266502900000001</v>
       </c>
       <c r="P83">
-        <v>24.94286835</v>
+        <v>24.7995087</v>
       </c>
       <c r="Q83">
-        <v>27.00286835</v>
+        <v>26.8595087</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3639391865033369</v>
+        <v>0.3805608785881507</v>
       </c>
       <c r="T83">
-        <v>4.921512034820882</v>
+        <v>5.178644325041409</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.1480008237764</v>
+        <v>3.109610569827907</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1079224581458671</v>
+        <v>0.1077557208561002</v>
       </c>
       <c r="C84">
-        <v>94.02360442007483</v>
+        <v>91.89458431973341</v>
       </c>
       <c r="D84">
-        <v>316.9476044200748</v>
+        <v>317.8005843197334</v>
       </c>
       <c r="E84">
-        <v>123.924</v>
+        <v>126.906</v>
       </c>
       <c r="F84">
-        <v>244.524</v>
+        <v>247.506</v>
       </c>
       <c r="G84">
         <v>21.6</v>
@@ -8169,28 +8169,28 @@
         <v>48.74</v>
       </c>
       <c r="M84">
-        <v>15.6739884</v>
+        <v>15.8651346</v>
       </c>
       <c r="N84">
-        <v>33.0660116</v>
+        <v>32.8748654</v>
       </c>
       <c r="O84">
-        <v>8.266502900000001</v>
+        <v>8.218716350000001</v>
       </c>
       <c r="P84">
-        <v>24.7995087</v>
+        <v>24.65614905</v>
       </c>
       <c r="Q84">
-        <v>26.8595087</v>
+        <v>26.71614905</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3805608785881507</v>
+        <v>0.3991380638594133</v>
       </c>
       <c r="T84">
-        <v>5.178644325041409</v>
+        <v>5.46602747293494</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.109610569827907</v>
+        <v>3.072145382239619</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1077557208561002</v>
+        <v>0.1075889835663334</v>
       </c>
       <c r="C85">
-        <v>91.89458431973341</v>
+        <v>89.77016774411382</v>
       </c>
       <c r="D85">
-        <v>317.8005843197334</v>
+        <v>318.6581677441138</v>
       </c>
       <c r="E85">
-        <v>126.906</v>
+        <v>129.888</v>
       </c>
       <c r="F85">
-        <v>247.506</v>
+        <v>250.488</v>
       </c>
       <c r="G85">
         <v>21.6</v>
@@ -8251,28 +8251,28 @@
         <v>48.74</v>
       </c>
       <c r="M85">
-        <v>15.8651346</v>
+        <v>16.0562808</v>
       </c>
       <c r="N85">
-        <v>32.8748654</v>
+        <v>32.6837192</v>
       </c>
       <c r="O85">
-        <v>8.218716350000001</v>
+        <v>8.1709298</v>
       </c>
       <c r="P85">
-        <v>24.65614905</v>
+        <v>24.5127894</v>
       </c>
       <c r="Q85">
-        <v>26.71614905</v>
+        <v>26.5727894</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3991380638594133</v>
+        <v>0.4200373972895837</v>
       </c>
       <c r="T85">
-        <v>5.46602747293494</v>
+        <v>5.789333514315161</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.072145382239619</v>
+        <v>3.035572222927242</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1075889835663334</v>
+        <v>0.1123947462765665</v>
       </c>
       <c r="C86">
-        <v>89.77016774411393</v>
+        <v>63.7924267062844</v>
       </c>
       <c r="D86">
-        <v>318.6581677441139</v>
+        <v>295.6624267062844</v>
       </c>
       <c r="E86">
-        <v>129.888</v>
+        <v>132.87</v>
       </c>
       <c r="F86">
-        <v>250.488</v>
+        <v>253.47</v>
       </c>
       <c r="G86">
         <v>21.6</v>
@@ -8333,45 +8333,45 @@
         <v>48.74</v>
       </c>
       <c r="M86">
-        <v>16.0562808</v>
+        <v>18.224493</v>
       </c>
       <c r="N86">
-        <v>32.6837192</v>
+        <v>30.515507</v>
       </c>
       <c r="O86">
-        <v>8.1709298</v>
+        <v>7.628876750000001</v>
       </c>
       <c r="P86">
-        <v>24.5127894</v>
+        <v>22.88663025</v>
       </c>
       <c r="Q86">
-        <v>26.5727894</v>
+        <v>24.94663025</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4200373972895834</v>
+        <v>0.4437233085104432</v>
       </c>
       <c r="T86">
-        <v>5.789333514315157</v>
+        <v>6.155747027879409</v>
       </c>
       <c r="U86">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V86">
         <v>0.25</v>
       </c>
       <c r="W86">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y86">
-        <v>3.035572222927242</v>
+        <v>2.674422822077958</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1123947462765665</v>
+        <v>0.1122865089867996</v>
       </c>
       <c r="C87">
-        <v>63.7924267062844</v>
+        <v>61.29175292178695</v>
       </c>
       <c r="D87">
-        <v>295.6624267062844</v>
+        <v>296.1437529217869</v>
       </c>
       <c r="E87">
-        <v>132.87</v>
+        <v>135.852</v>
       </c>
       <c r="F87">
-        <v>253.47</v>
+        <v>256.452</v>
       </c>
       <c r="G87">
         <v>21.6</v>
@@ -8415,28 +8415,28 @@
         <v>48.74</v>
       </c>
       <c r="M87">
-        <v>18.224493</v>
+        <v>18.4388988</v>
       </c>
       <c r="N87">
-        <v>30.515507</v>
+        <v>30.3011012</v>
       </c>
       <c r="O87">
-        <v>7.628876750000001</v>
+        <v>7.5752753</v>
       </c>
       <c r="P87">
-        <v>22.88663025</v>
+        <v>22.7258259</v>
       </c>
       <c r="Q87">
-        <v>24.94663025</v>
+        <v>24.7858259</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4437233085104432</v>
+        <v>0.4707929213342829</v>
       </c>
       <c r="T87">
-        <v>6.155747027879409</v>
+        <v>6.574505329095695</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.674422822077958</v>
+        <v>2.643324882286354</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1122865089867996</v>
+        <v>0.1121782716970327</v>
       </c>
       <c r="C88">
-        <v>61.29175292178695</v>
+        <v>58.79264885110484</v>
       </c>
       <c r="D88">
-        <v>296.1437529217869</v>
+        <v>296.6266488511048</v>
       </c>
       <c r="E88">
-        <v>135.852</v>
+        <v>138.834</v>
       </c>
       <c r="F88">
-        <v>256.452</v>
+        <v>259.434</v>
       </c>
       <c r="G88">
         <v>21.6</v>
@@ -8497,28 +8497,28 @@
         <v>48.74</v>
       </c>
       <c r="M88">
-        <v>18.4388988</v>
+        <v>18.6533046</v>
       </c>
       <c r="N88">
-        <v>30.3011012</v>
+        <v>30.0866954</v>
       </c>
       <c r="O88">
-        <v>7.5752753</v>
+        <v>7.521673850000001</v>
       </c>
       <c r="P88">
-        <v>22.7258259</v>
+        <v>22.56502155</v>
       </c>
       <c r="Q88">
-        <v>24.7858259</v>
+        <v>24.62502155</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4707929213342829</v>
+        <v>0.5020270899771747</v>
       </c>
       <c r="T88">
-        <v>6.574505329095695</v>
+        <v>7.057687984345255</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.643324882286354</v>
+        <v>2.612941837662373</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1121782716970327</v>
+        <v>0.1120700344072658</v>
       </c>
       <c r="C89">
-        <v>58.79264885110484</v>
+        <v>56.29512218556789</v>
       </c>
       <c r="D89">
-        <v>296.6266488511048</v>
+        <v>297.1111221855679</v>
       </c>
       <c r="E89">
-        <v>138.834</v>
+        <v>141.816</v>
       </c>
       <c r="F89">
-        <v>259.434</v>
+        <v>262.416</v>
       </c>
       <c r="G89">
         <v>21.6</v>
@@ -8579,28 +8579,28 @@
         <v>48.74</v>
       </c>
       <c r="M89">
-        <v>18.6533046</v>
+        <v>18.8677104</v>
       </c>
       <c r="N89">
-        <v>30.0866954</v>
+        <v>29.8722896</v>
       </c>
       <c r="O89">
-        <v>7.521673850000001</v>
+        <v>7.4680724</v>
       </c>
       <c r="P89">
-        <v>22.56502155</v>
+        <v>22.4042172</v>
       </c>
       <c r="Q89">
-        <v>24.62502155</v>
+        <v>24.4642172</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5020270899771747</v>
+        <v>0.5384669533938821</v>
       </c>
       <c r="T89">
-        <v>7.057687984345255</v>
+        <v>7.621401082136411</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.612941837662373</v>
+        <v>2.583249316779846</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1120700344072658</v>
+        <v>0.111961797117499</v>
       </c>
       <c r="C90">
-        <v>56.29512218556789</v>
+        <v>53.79918066683695</v>
       </c>
       <c r="D90">
-        <v>297.1111221855679</v>
+        <v>297.5971806668369</v>
       </c>
       <c r="E90">
-        <v>141.816</v>
+        <v>144.798</v>
       </c>
       <c r="F90">
-        <v>262.416</v>
+        <v>265.398</v>
       </c>
       <c r="G90">
         <v>21.6</v>
@@ -8661,28 +8661,28 @@
         <v>48.74</v>
       </c>
       <c r="M90">
-        <v>18.8677104</v>
+        <v>19.0821162</v>
       </c>
       <c r="N90">
-        <v>29.8722896</v>
+        <v>29.6578838</v>
       </c>
       <c r="O90">
-        <v>7.4680724</v>
+        <v>7.414470950000001</v>
       </c>
       <c r="P90">
-        <v>22.4042172</v>
+        <v>22.24341285</v>
       </c>
       <c r="Q90">
-        <v>24.4642172</v>
+        <v>24.30341285</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5384669533938821</v>
+        <v>0.581532246522718</v>
       </c>
       <c r="T90">
-        <v>7.621401082136411</v>
+        <v>8.287607470435049</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.583249316779846</v>
+        <v>2.554224043557601</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.111961797117499</v>
+        <v>0.1118535598277321</v>
       </c>
       <c r="C91">
-        <v>53.79918066683695</v>
+        <v>51.30483208731522</v>
       </c>
       <c r="D91">
-        <v>297.5971806668369</v>
+        <v>298.0848320873152</v>
       </c>
       <c r="E91">
-        <v>144.798</v>
+        <v>147.78</v>
       </c>
       <c r="F91">
-        <v>265.398</v>
+        <v>268.38</v>
       </c>
       <c r="G91">
         <v>21.6</v>
@@ -8743,28 +8743,28 @@
         <v>48.74</v>
       </c>
       <c r="M91">
-        <v>19.0821162</v>
+        <v>19.296522</v>
       </c>
       <c r="N91">
-        <v>29.6578838</v>
+        <v>29.443478</v>
       </c>
       <c r="O91">
-        <v>7.414470950000001</v>
+        <v>7.360869500000001</v>
       </c>
       <c r="P91">
-        <v>22.24341285</v>
+        <v>22.0826085</v>
       </c>
       <c r="Q91">
-        <v>24.30341285</v>
+        <v>24.1426085</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.581532246522718</v>
+        <v>0.6332105982773211</v>
       </c>
       <c r="T91">
-        <v>8.287607470435049</v>
+        <v>9.087055136393415</v>
       </c>
       <c r="U91">
         <v>0.07190000000000001</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.554224043557601</v>
+        <v>2.525843776406961</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1118535598277321</v>
+        <v>0.1144070725379652</v>
       </c>
       <c r="C92">
-        <v>51.30483208731522</v>
+        <v>37.22829942027181</v>
       </c>
       <c r="D92">
-        <v>298.0848320873152</v>
+        <v>286.9902994202718</v>
       </c>
       <c r="E92">
-        <v>147.78</v>
+        <v>150.762</v>
       </c>
       <c r="F92">
-        <v>268.38</v>
+        <v>271.362</v>
       </c>
       <c r="G92">
         <v>21.6</v>
@@ -8825,45 +8825,45 @@
         <v>48.74</v>
       </c>
       <c r="M92">
-        <v>19.296522</v>
+        <v>20.5692396</v>
       </c>
       <c r="N92">
-        <v>29.443478</v>
+        <v>28.1707604</v>
       </c>
       <c r="O92">
-        <v>7.360869500000001</v>
+        <v>7.0426901</v>
       </c>
       <c r="P92">
-        <v>22.0826085</v>
+        <v>21.1280703</v>
       </c>
       <c r="Q92">
-        <v>24.1426085</v>
+        <v>23.1880703</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6332105982773211</v>
+        <v>0.6963730281996137</v>
       </c>
       <c r="T92">
-        <v>9.087055136393415</v>
+        <v>10.06415783923142</v>
       </c>
       <c r="U92">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V92">
         <v>0.25</v>
       </c>
       <c r="W92">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y92">
-        <v>2.525843776406961</v>
+        <v>2.369557696240749</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1144070725379652</v>
+        <v>0.1143280852481983</v>
       </c>
       <c r="C93">
-        <v>37.22829942027181</v>
+        <v>34.57709205599912</v>
       </c>
       <c r="D93">
-        <v>286.9902994202718</v>
+        <v>287.3210920559991</v>
       </c>
       <c r="E93">
-        <v>150.762</v>
+        <v>153.744</v>
       </c>
       <c r="F93">
-        <v>271.362</v>
+        <v>274.344</v>
       </c>
       <c r="G93">
         <v>21.6</v>
@@ -8907,28 +8907,28 @@
         <v>48.74</v>
       </c>
       <c r="M93">
-        <v>20.5692396</v>
+        <v>20.7952752</v>
       </c>
       <c r="N93">
-        <v>28.1707604</v>
+        <v>27.9447248</v>
       </c>
       <c r="O93">
-        <v>7.0426901</v>
+        <v>6.9861812</v>
       </c>
       <c r="P93">
-        <v>21.1280703</v>
+        <v>20.9585436</v>
       </c>
       <c r="Q93">
-        <v>23.1880703</v>
+        <v>23.0185436</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6963730281996137</v>
+        <v>0.7753260656024796</v>
       </c>
       <c r="T93">
-        <v>10.06415783923142</v>
+        <v>11.28553621777892</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.369557696240749</v>
+        <v>2.343801634325089</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1143280852481983</v>
+        <v>0.1142490979584315</v>
       </c>
       <c r="C94">
-        <v>34.57709205599912</v>
+        <v>31.92664813243044</v>
       </c>
       <c r="D94">
-        <v>287.3210920559991</v>
+        <v>287.6526481324304</v>
       </c>
       <c r="E94">
-        <v>153.744</v>
+        <v>156.726</v>
       </c>
       <c r="F94">
-        <v>274.344</v>
+        <v>277.326</v>
       </c>
       <c r="G94">
         <v>21.6</v>
@@ -8989,28 +8989,28 @@
         <v>48.74</v>
       </c>
       <c r="M94">
-        <v>20.7952752</v>
+        <v>21.0213108</v>
       </c>
       <c r="N94">
-        <v>27.9447248</v>
+        <v>27.7186892</v>
       </c>
       <c r="O94">
-        <v>6.9861812</v>
+        <v>6.9296723</v>
       </c>
       <c r="P94">
-        <v>20.9585436</v>
+        <v>20.7890169</v>
       </c>
       <c r="Q94">
-        <v>23.0185436</v>
+        <v>22.8490169</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7753260656024796</v>
+        <v>0.8768371136918786</v>
       </c>
       <c r="T94">
-        <v>11.28553621777892</v>
+        <v>12.85587984734</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.343801634325089</v>
+        <v>2.318599466214067</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1142490979584315</v>
+        <v>0.1141701106686646</v>
       </c>
       <c r="C95">
-        <v>31.92664813243044</v>
+        <v>29.27697029555173</v>
       </c>
       <c r="D95">
-        <v>287.6526481324304</v>
+        <v>287.9849702955517</v>
       </c>
       <c r="E95">
-        <v>156.726</v>
+        <v>159.708</v>
       </c>
       <c r="F95">
-        <v>277.326</v>
+        <v>280.308</v>
       </c>
       <c r="G95">
         <v>21.6</v>
@@ -9071,28 +9071,28 @@
         <v>48.74</v>
       </c>
       <c r="M95">
-        <v>21.0213108</v>
+        <v>21.2473464</v>
       </c>
       <c r="N95">
-        <v>27.7186892</v>
+        <v>27.4926536</v>
       </c>
       <c r="O95">
-        <v>6.9296723</v>
+        <v>6.8731634</v>
       </c>
       <c r="P95">
-        <v>20.7890169</v>
+        <v>20.6194902</v>
       </c>
       <c r="Q95">
-        <v>22.8490169</v>
+        <v>22.6794902</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8768371136918786</v>
+        <v>1.012185177811077</v>
       </c>
       <c r="T95">
-        <v>12.85587984734</v>
+        <v>14.94967135342143</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.318599466214067</v>
+        <v>2.293933514445832</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1141701106686646</v>
+        <v>0.1140911233788977</v>
       </c>
       <c r="C96">
-        <v>29.27697029555173</v>
+        <v>26.62806120359005</v>
       </c>
       <c r="D96">
-        <v>287.9849702955517</v>
+        <v>288.31806120359</v>
       </c>
       <c r="E96">
-        <v>159.708</v>
+        <v>162.69</v>
       </c>
       <c r="F96">
-        <v>280.308</v>
+        <v>283.29</v>
       </c>
       <c r="G96">
         <v>21.6</v>
@@ -9153,28 +9153,28 @@
         <v>48.74</v>
       </c>
       <c r="M96">
-        <v>21.2473464</v>
+        <v>21.473382</v>
       </c>
       <c r="N96">
-        <v>27.4926536</v>
+        <v>27.266618</v>
       </c>
       <c r="O96">
-        <v>6.8731634</v>
+        <v>6.816654499999999</v>
       </c>
       <c r="P96">
-        <v>20.6194902</v>
+        <v>20.4499635</v>
       </c>
       <c r="Q96">
-        <v>22.6794902</v>
+        <v>22.5099635</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.012185177811077</v>
+        <v>1.201672467577956</v>
       </c>
       <c r="T96">
-        <v>14.94967135342143</v>
+        <v>17.88097946193545</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.293933514445832</v>
+        <v>2.269786845872718</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1140911233788977</v>
+        <v>0.1140121360891308</v>
       </c>
       <c r="C97">
-        <v>26.62806120359005</v>
+        <v>23.97992352708565</v>
       </c>
       <c r="D97">
-        <v>288.31806120359</v>
+        <v>288.6519235270856</v>
       </c>
       <c r="E97">
-        <v>162.69</v>
+        <v>165.672</v>
       </c>
       <c r="F97">
-        <v>283.29</v>
+        <v>286.272</v>
       </c>
       <c r="G97">
         <v>21.6</v>
@@ -9235,28 +9235,28 @@
         <v>48.74</v>
       </c>
       <c r="M97">
-        <v>21.473382</v>
+        <v>21.6994176</v>
       </c>
       <c r="N97">
-        <v>27.266618</v>
+        <v>27.0405824</v>
       </c>
       <c r="O97">
-        <v>6.816654499999999</v>
+        <v>6.7601456</v>
       </c>
       <c r="P97">
-        <v>20.4499635</v>
+        <v>20.2804368</v>
       </c>
       <c r="Q97">
-        <v>22.5099635</v>
+        <v>22.3404368</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.201672467577956</v>
+        <v>1.485903402228273</v>
       </c>
       <c r="T97">
-        <v>17.88097946193545</v>
+        <v>22.27794162470647</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.269786845872718</v>
+        <v>2.246143232894878</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1140121360891308</v>
+        <v>0.113933148799364</v>
       </c>
       <c r="C98">
-        <v>23.97992352708565</v>
+        <v>21.33255994896211</v>
       </c>
       <c r="D98">
-        <v>288.6519235270856</v>
+        <v>288.9865599489621</v>
       </c>
       <c r="E98">
-        <v>165.672</v>
+        <v>168.654</v>
       </c>
       <c r="F98">
-        <v>286.272</v>
+        <v>289.254</v>
       </c>
       <c r="G98">
         <v>21.6</v>
@@ -9317,28 +9317,28 @@
         <v>48.74</v>
       </c>
       <c r="M98">
-        <v>21.6994176</v>
+        <v>21.9254532</v>
       </c>
       <c r="N98">
-        <v>27.0405824</v>
+        <v>26.8145468</v>
       </c>
       <c r="O98">
-        <v>6.7601456</v>
+        <v>6.703636700000001</v>
       </c>
       <c r="P98">
-        <v>20.2804368</v>
+        <v>20.1109101</v>
       </c>
       <c r="Q98">
-        <v>22.3404368</v>
+        <v>22.1709101</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.48590340222827</v>
+        <v>1.959621626645464</v>
       </c>
       <c r="T98">
-        <v>22.27794162470641</v>
+        <v>29.60621189599142</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.246143232894878</v>
+        <v>2.222987117091837</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.113933148799364</v>
+        <v>0.1138541615095971</v>
       </c>
       <c r="C99">
-        <v>21.33255994896211</v>
+        <v>18.68597316459932</v>
       </c>
       <c r="D99">
-        <v>288.9865599489621</v>
+        <v>289.3219731645993</v>
       </c>
       <c r="E99">
-        <v>168.654</v>
+        <v>171.636</v>
       </c>
       <c r="F99">
-        <v>289.254</v>
+        <v>292.236</v>
       </c>
       <c r="G99">
         <v>21.6</v>
@@ -9399,28 +9399,28 @@
         <v>48.74</v>
       </c>
       <c r="M99">
-        <v>21.9254532</v>
+        <v>22.1514888</v>
       </c>
       <c r="N99">
-        <v>26.8145468</v>
+        <v>26.5885112</v>
       </c>
       <c r="O99">
-        <v>6.703636700000001</v>
+        <v>6.6471278</v>
       </c>
       <c r="P99">
-        <v>20.1109101</v>
+        <v>19.9413834</v>
       </c>
       <c r="Q99">
-        <v>22.1709101</v>
+        <v>22.0013834</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.959621626645464</v>
+        <v>2.907058075479851</v>
       </c>
       <c r="T99">
-        <v>29.60621189599142</v>
+        <v>44.26275243856143</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.222987117091837</v>
+        <v>2.200303575080696</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1138541615095971</v>
+        <v>0.1137751742198302</v>
       </c>
       <c r="C100">
-        <v>18.68597316459932</v>
+        <v>16.04016588190473</v>
       </c>
       <c r="D100">
-        <v>289.3219731645993</v>
+        <v>289.6581658819047</v>
       </c>
       <c r="E100">
-        <v>171.636</v>
+        <v>174.618</v>
       </c>
       <c r="F100">
-        <v>292.236</v>
+        <v>295.218</v>
       </c>
       <c r="G100">
         <v>21.6</v>
@@ -9481,28 +9481,28 @@
         <v>48.74</v>
       </c>
       <c r="M100">
-        <v>22.1514888</v>
+        <v>22.3775244</v>
       </c>
       <c r="N100">
-        <v>26.5885112</v>
+        <v>26.3624756</v>
       </c>
       <c r="O100">
-        <v>6.6471278</v>
+        <v>6.590618900000001</v>
       </c>
       <c r="P100">
-        <v>19.9413834</v>
+        <v>19.7718567</v>
       </c>
       <c r="Q100">
-        <v>22.0013834</v>
+        <v>21.8318567</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.907058075479851</v>
+        <v>5.749367421983015</v>
       </c>
       <c r="T100">
-        <v>44.26275243856143</v>
+        <v>88.23237406627146</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.200303575080696</v>
+        <v>2.178078286443518</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1137751742198302</v>
-      </c>
-      <c r="C101">
-        <v>16.04016588190473</v>
-      </c>
-      <c r="D101">
-        <v>289.6581658819047</v>
-      </c>
-      <c r="E101">
-        <v>174.618</v>
-      </c>
-      <c r="F101">
-        <v>295.218</v>
-      </c>
-      <c r="G101">
-        <v>21.6</v>
-      </c>
-      <c r="H101">
-        <v>177.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>50.8</v>
-      </c>
-      <c r="K101">
-        <v>2.06</v>
-      </c>
-      <c r="L101">
-        <v>48.74</v>
-      </c>
-      <c r="M101">
-        <v>22.3775244</v>
-      </c>
-      <c r="N101">
-        <v>26.3624756</v>
-      </c>
-      <c r="O101">
-        <v>6.590618900000001</v>
-      </c>
-      <c r="P101">
-        <v>19.7718567</v>
-      </c>
-      <c r="Q101">
-        <v>21.8318567</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.749367421983015</v>
-      </c>
-      <c r="T101">
-        <v>88.23237406627146</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.05685</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.178078286443518</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
